--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120970942</v>
+        <v>120976759</v>
       </c>
       <c r="B20" t="n">
-        <v>79639</v>
+        <v>78598</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,38 +2682,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387010</v>
+        <v>388030</v>
       </c>
       <c r="R20" t="n">
-        <v>6723330</v>
+        <v>6723650</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2760,22 +2760,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120976759</v>
+        <v>120970942</v>
       </c>
       <c r="B21" t="n">
-        <v>78598</v>
+        <v>79639</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2784,38 +2784,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>388030</v>
+        <v>387010</v>
       </c>
       <c r="R21" t="n">
-        <v>6723650</v>
+        <v>6723330</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,22 +2862,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120976735</v>
+        <v>120970931</v>
       </c>
       <c r="B22" t="n">
-        <v>90652</v>
+        <v>95618</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2886,38 +2886,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387303</v>
+        <v>387533</v>
       </c>
       <c r="R22" t="n">
-        <v>6723425</v>
+        <v>6723413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2964,22 +2964,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120970931</v>
+        <v>120976743</v>
       </c>
       <c r="B23" t="n">
-        <v>95618</v>
+        <v>78632</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2992,34 +2992,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>387533</v>
+        <v>387788</v>
       </c>
       <c r="R23" t="n">
-        <v>6723413</v>
+        <v>6723519</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,22 +3066,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120976743</v>
+        <v>120976735</v>
       </c>
       <c r="B24" t="n">
-        <v>78632</v>
+        <v>90652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3090,25 +3090,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387788</v>
+        <v>387303</v>
       </c>
       <c r="R24" t="n">
-        <v>6723519</v>
+        <v>6723425</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120970923</v>
+        <v>120976748</v>
       </c>
       <c r="B28" t="n">
-        <v>78632</v>
+        <v>78598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3502,34 +3502,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387857</v>
+        <v>387836</v>
       </c>
       <c r="R28" t="n">
-        <v>6723518</v>
+        <v>6723530</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3576,22 +3576,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120976748</v>
+        <v>120970923</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>78632</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3604,34 +3604,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387836</v>
+        <v>387857</v>
       </c>
       <c r="R29" t="n">
-        <v>6723530</v>
+        <v>6723518</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,12 +3678,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120970928</v>
+        <v>120976746</v>
       </c>
       <c r="B53" t="n">
-        <v>82382</v>
+        <v>78632</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6052,34 +6052,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387650</v>
+        <v>387815</v>
       </c>
       <c r="R53" t="n">
-        <v>6723547</v>
+        <v>6723536</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6126,22 +6126,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120976746</v>
+        <v>120970920</v>
       </c>
       <c r="B54" t="n">
-        <v>78632</v>
+        <v>78598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6154,34 +6154,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387815</v>
+        <v>388053</v>
       </c>
       <c r="R54" t="n">
-        <v>6723536</v>
+        <v>6723664</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6228,22 +6228,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120970920</v>
+        <v>120970928</v>
       </c>
       <c r="B55" t="n">
-        <v>78598</v>
+        <v>82382</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>388053</v>
+        <v>387650</v>
       </c>
       <c r="R55" t="n">
-        <v>6723664</v>
+        <v>6723547</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -2262,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120976760</v>
+        <v>120970937</v>
       </c>
       <c r="B16" t="n">
-        <v>95618</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,34 +2278,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388074</v>
+        <v>386898</v>
       </c>
       <c r="R16" t="n">
-        <v>6723700</v>
+        <v>6723285</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,22 +2352,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120970934</v>
+        <v>120970939</v>
       </c>
       <c r="B17" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,25 +2376,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387036</v>
+        <v>386858</v>
       </c>
       <c r="R17" t="n">
-        <v>6723319</v>
+        <v>6723265</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120976736</v>
+        <v>120976755</v>
       </c>
       <c r="B18" t="n">
-        <v>88018</v>
+        <v>78635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2482,21 +2482,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387487</v>
+        <v>387971</v>
       </c>
       <c r="R18" t="n">
-        <v>6723421</v>
+        <v>6723631</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120970926</v>
+        <v>120970928</v>
       </c>
       <c r="B19" t="n">
-        <v>78632</v>
+        <v>82385</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2584,21 +2584,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387809</v>
+        <v>387650</v>
       </c>
       <c r="R19" t="n">
-        <v>6723508</v>
+        <v>6723547</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120976759</v>
+        <v>120976748</v>
       </c>
       <c r="B20" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>388030</v>
+        <v>387836</v>
       </c>
       <c r="R20" t="n">
-        <v>6723650</v>
+        <v>6723530</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120970942</v>
+        <v>120976727</v>
       </c>
       <c r="B21" t="n">
-        <v>79639</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2784,38 +2784,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387010</v>
+        <v>386876</v>
       </c>
       <c r="R21" t="n">
-        <v>6723330</v>
+        <v>6723260</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,22 +2862,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120970931</v>
+        <v>120976756</v>
       </c>
       <c r="B22" t="n">
-        <v>95618</v>
+        <v>78635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2890,34 +2890,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387533</v>
+        <v>387997</v>
       </c>
       <c r="R22" t="n">
-        <v>6723413</v>
+        <v>6723622</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2964,22 +2964,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120976743</v>
+        <v>120976738</v>
       </c>
       <c r="B23" t="n">
-        <v>78632</v>
+        <v>82385</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>387788</v>
+        <v>387659</v>
       </c>
       <c r="R23" t="n">
-        <v>6723519</v>
+        <v>6723515</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120976735</v>
+        <v>120970942</v>
       </c>
       <c r="B24" t="n">
-        <v>90652</v>
+        <v>79642</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3094,34 +3094,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387303</v>
+        <v>387010</v>
       </c>
       <c r="R24" t="n">
-        <v>6723425</v>
+        <v>6723330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,22 +3168,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120976726</v>
+        <v>120976747</v>
       </c>
       <c r="B25" t="n">
-        <v>82382</v>
+        <v>90662</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,25 +3192,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387454</v>
+        <v>387814</v>
       </c>
       <c r="R25" t="n">
-        <v>6723442</v>
+        <v>6723543</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120970936</v>
+        <v>120970923</v>
       </c>
       <c r="B26" t="n">
-        <v>78598</v>
+        <v>78635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,21 +3298,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>386940</v>
+        <v>387857</v>
       </c>
       <c r="R26" t="n">
-        <v>6723292</v>
+        <v>6723518</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120970940</v>
+        <v>120976758</v>
       </c>
       <c r="B27" t="n">
-        <v>79708</v>
+        <v>78635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3396,38 +3396,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387010</v>
+        <v>388026</v>
       </c>
       <c r="R27" t="n">
-        <v>6723330</v>
+        <v>6723646</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3474,22 +3474,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120976748</v>
+        <v>120976741</v>
       </c>
       <c r="B28" t="n">
-        <v>78598</v>
+        <v>78635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3502,21 +3502,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387836</v>
+        <v>387768</v>
       </c>
       <c r="R28" t="n">
-        <v>6723530</v>
+        <v>6723513</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120970923</v>
+        <v>120976745</v>
       </c>
       <c r="B29" t="n">
-        <v>78632</v>
+        <v>78635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3624,14 +3624,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387857</v>
+        <v>387797</v>
       </c>
       <c r="R29" t="n">
-        <v>6723518</v>
+        <v>6723537</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,22 +3678,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120970921</v>
+        <v>120976740</v>
       </c>
       <c r="B30" t="n">
-        <v>78632</v>
+        <v>80558</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3706,34 +3706,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387966</v>
+        <v>387671</v>
       </c>
       <c r="R30" t="n">
-        <v>6723628</v>
+        <v>6723531</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3780,22 +3780,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120970945</v>
+        <v>120976746</v>
       </c>
       <c r="B31" t="n">
-        <v>90652</v>
+        <v>78635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3804,38 +3804,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387254</v>
+        <v>387815</v>
       </c>
       <c r="R31" t="n">
-        <v>6723421</v>
+        <v>6723536</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3882,12 +3882,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3897,7 +3897,7 @@
         <v>120970922</v>
       </c>
       <c r="B32" t="n">
-        <v>78632</v>
+        <v>78635</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120976741</v>
+        <v>120976734</v>
       </c>
       <c r="B33" t="n">
-        <v>78632</v>
+        <v>78338</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4012,21 +4012,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387768</v>
+        <v>387161</v>
       </c>
       <c r="R33" t="n">
-        <v>6723513</v>
+        <v>6723401</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4098,10 +4098,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120970927</v>
+        <v>120976749</v>
       </c>
       <c r="B34" t="n">
-        <v>78632</v>
+        <v>82385</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4114,34 +4114,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387791</v>
+        <v>387877</v>
       </c>
       <c r="R34" t="n">
-        <v>6723505</v>
+        <v>6723565</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,22 +4188,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120970930</v>
+        <v>120976742</v>
       </c>
       <c r="B35" t="n">
-        <v>82382</v>
+        <v>74692</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4212,38 +4212,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>387646</v>
+        <v>387783</v>
       </c>
       <c r="R35" t="n">
-        <v>6723530</v>
+        <v>6723518</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,22 +4290,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120976730</v>
+        <v>120970933</v>
       </c>
       <c r="B36" t="n">
-        <v>82382</v>
+        <v>79642</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,38 +4314,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>386895</v>
+        <v>387048</v>
       </c>
       <c r="R36" t="n">
-        <v>6723208</v>
+        <v>6723350</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4392,22 +4392,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120976745</v>
+        <v>120976731</v>
       </c>
       <c r="B37" t="n">
-        <v>78632</v>
+        <v>88024</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4420,21 +4420,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387797</v>
+        <v>386893</v>
       </c>
       <c r="R37" t="n">
-        <v>6723537</v>
+        <v>6723204</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4506,10 +4506,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120976752</v>
+        <v>120976757</v>
       </c>
       <c r="B38" t="n">
-        <v>78632</v>
+        <v>78601</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387969</v>
+        <v>388006</v>
       </c>
       <c r="R38" t="n">
-        <v>6723628</v>
+        <v>6723626</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120970948</v>
+        <v>120970926</v>
       </c>
       <c r="B39" t="n">
-        <v>88018</v>
+        <v>78635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4624,21 +4624,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387470</v>
+        <v>387809</v>
       </c>
       <c r="R39" t="n">
-        <v>6723459</v>
+        <v>6723508</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4710,10 +4710,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120976756</v>
+        <v>120970948</v>
       </c>
       <c r="B40" t="n">
-        <v>78632</v>
+        <v>88024</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4726,34 +4726,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387997</v>
+        <v>387470</v>
       </c>
       <c r="R40" t="n">
-        <v>6723622</v>
+        <v>6723459</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,22 +4800,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120970937</v>
+        <v>120970921</v>
       </c>
       <c r="B41" t="n">
-        <v>78598</v>
+        <v>78635</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>386898</v>
+        <v>387966</v>
       </c>
       <c r="R41" t="n">
-        <v>6723285</v>
+        <v>6723628</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4914,10 +4914,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120976749</v>
+        <v>120970931</v>
       </c>
       <c r="B42" t="n">
-        <v>82382</v>
+        <v>95628</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4930,34 +4930,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387877</v>
+        <v>387533</v>
       </c>
       <c r="R42" t="n">
-        <v>6723565</v>
+        <v>6723413</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5004,22 +5004,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120970943</v>
+        <v>120976730</v>
       </c>
       <c r="B43" t="n">
-        <v>79708</v>
+        <v>82385</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5028,38 +5028,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387078</v>
+        <v>386895</v>
       </c>
       <c r="R43" t="n">
-        <v>6723335</v>
+        <v>6723208</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5106,22 +5106,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120970924</v>
+        <v>120970936</v>
       </c>
       <c r="B44" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387816</v>
+        <v>386940</v>
       </c>
       <c r="R44" t="n">
-        <v>6723527</v>
+        <v>6723292</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120976742</v>
+        <v>120976744</v>
       </c>
       <c r="B45" t="n">
-        <v>74689</v>
+        <v>78601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5232,25 +5232,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387783</v>
+        <v>387795</v>
       </c>
       <c r="R45" t="n">
-        <v>6723518</v>
+        <v>6723523</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120976758</v>
+        <v>120976759</v>
       </c>
       <c r="B46" t="n">
-        <v>78632</v>
+        <v>78601</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5338,21 +5338,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>388026</v>
+        <v>388030</v>
       </c>
       <c r="R46" t="n">
-        <v>6723646</v>
+        <v>6723650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5424,10 +5424,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120970933</v>
+        <v>120976754</v>
       </c>
       <c r="B47" t="n">
-        <v>79639</v>
+        <v>88024</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5436,38 +5436,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387048</v>
+        <v>387963</v>
       </c>
       <c r="R47" t="n">
-        <v>6723350</v>
+        <v>6723633</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5514,12 +5514,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5529,7 +5529,7 @@
         <v>120970925</v>
       </c>
       <c r="B48" t="n">
-        <v>78632</v>
+        <v>78635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5628,10 +5628,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120976738</v>
+        <v>120970943</v>
       </c>
       <c r="B49" t="n">
-        <v>82382</v>
+        <v>79711</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5640,38 +5640,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387659</v>
+        <v>387078</v>
       </c>
       <c r="R49" t="n">
-        <v>6723515</v>
+        <v>6723335</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5718,22 +5718,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120976740</v>
+        <v>120970934</v>
       </c>
       <c r="B50" t="n">
-        <v>80555</v>
+        <v>90662</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5742,38 +5742,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>387671</v>
+        <v>387036</v>
       </c>
       <c r="R50" t="n">
-        <v>6723531</v>
+        <v>6723319</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5820,22 +5820,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120970946</v>
+        <v>120970945</v>
       </c>
       <c r="B51" t="n">
-        <v>88018</v>
+        <v>90662</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5844,25 +5844,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>387338</v>
+        <v>387254</v>
       </c>
       <c r="R51" t="n">
-        <v>6723431</v>
+        <v>6723421</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5934,10 +5934,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120976747</v>
+        <v>120976728</v>
       </c>
       <c r="B52" t="n">
-        <v>90652</v>
+        <v>88024</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5946,25 +5946,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>387814</v>
+        <v>386791</v>
       </c>
       <c r="R52" t="n">
-        <v>6723543</v>
+        <v>6723204</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6036,10 +6036,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120976746</v>
+        <v>120976743</v>
       </c>
       <c r="B53" t="n">
-        <v>78632</v>
+        <v>78635</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387815</v>
+        <v>387788</v>
       </c>
       <c r="R53" t="n">
-        <v>6723536</v>
+        <v>6723519</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120970920</v>
+        <v>120976760</v>
       </c>
       <c r="B54" t="n">
-        <v>78598</v>
+        <v>95628</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6154,34 +6154,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>388053</v>
+        <v>388074</v>
       </c>
       <c r="R54" t="n">
-        <v>6723664</v>
+        <v>6723700</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6228,22 +6228,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120970928</v>
+        <v>120970920</v>
       </c>
       <c r="B55" t="n">
-        <v>82382</v>
+        <v>78601</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387650</v>
+        <v>388053</v>
       </c>
       <c r="R55" t="n">
-        <v>6723547</v>
+        <v>6723664</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6342,10 +6342,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120976754</v>
+        <v>120976752</v>
       </c>
       <c r="B56" t="n">
-        <v>88018</v>
+        <v>78635</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6358,21 +6358,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387963</v>
+        <v>387969</v>
       </c>
       <c r="R56" t="n">
-        <v>6723633</v>
+        <v>6723628</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6444,10 +6444,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120976757</v>
+        <v>120970927</v>
       </c>
       <c r="B57" t="n">
-        <v>78598</v>
+        <v>78635</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6460,34 +6460,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>388006</v>
+        <v>387791</v>
       </c>
       <c r="R57" t="n">
-        <v>6723626</v>
+        <v>6723505</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6534,22 +6534,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120970939</v>
+        <v>120976751</v>
       </c>
       <c r="B58" t="n">
-        <v>78598</v>
+        <v>79219</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6562,34 +6562,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>386858</v>
+        <v>387955</v>
       </c>
       <c r="R58" t="n">
-        <v>6723265</v>
+        <v>6723604</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6636,22 +6636,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120976728</v>
+        <v>120970930</v>
       </c>
       <c r="B59" t="n">
-        <v>88018</v>
+        <v>82385</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6664,34 +6664,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>386791</v>
+        <v>387646</v>
       </c>
       <c r="R59" t="n">
-        <v>6723204</v>
+        <v>6723530</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6738,22 +6738,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120976751</v>
+        <v>120976726</v>
       </c>
       <c r="B60" t="n">
-        <v>79216</v>
+        <v>82385</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6766,21 +6766,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>387955</v>
+        <v>387454</v>
       </c>
       <c r="R60" t="n">
-        <v>6723604</v>
+        <v>6723442</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6852,10 +6852,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120976731</v>
+        <v>120970940</v>
       </c>
       <c r="B61" t="n">
-        <v>88018</v>
+        <v>79711</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6864,38 +6864,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>386893</v>
+        <v>387010</v>
       </c>
       <c r="R61" t="n">
-        <v>6723204</v>
+        <v>6723330</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6942,22 +6942,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120976755</v>
+        <v>120976735</v>
       </c>
       <c r="B62" t="n">
-        <v>78632</v>
+        <v>90662</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6966,25 +6966,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6994,10 +6994,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>387971</v>
+        <v>387303</v>
       </c>
       <c r="R62" t="n">
-        <v>6723631</v>
+        <v>6723425</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7056,10 +7056,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120976744</v>
+        <v>120970924</v>
       </c>
       <c r="B63" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7092,14 +7092,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>387795</v>
+        <v>387816</v>
       </c>
       <c r="R63" t="n">
-        <v>6723523</v>
+        <v>6723527</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7146,22 +7146,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120976727</v>
+        <v>120970946</v>
       </c>
       <c r="B64" t="n">
-        <v>78598</v>
+        <v>88024</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7174,34 +7174,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>386876</v>
+        <v>387338</v>
       </c>
       <c r="R64" t="n">
-        <v>6723260</v>
+        <v>6723431</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7248,22 +7248,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120976734</v>
+        <v>120976736</v>
       </c>
       <c r="B65" t="n">
-        <v>78335</v>
+        <v>88024</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7276,21 +7276,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>510</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7300,10 +7300,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>387161</v>
+        <v>387487</v>
       </c>
       <c r="R65" t="n">
-        <v>6723401</v>
+        <v>6723421</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -2466,10 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120976755</v>
+        <v>120970928</v>
       </c>
       <c r="B18" t="n">
-        <v>78635</v>
+        <v>82385</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2482,34 +2482,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387971</v>
+        <v>387650</v>
       </c>
       <c r="R18" t="n">
-        <v>6723631</v>
+        <v>6723547</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,22 +2556,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120970928</v>
+        <v>120976755</v>
       </c>
       <c r="B19" t="n">
-        <v>82385</v>
+        <v>78635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2584,34 +2584,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387650</v>
+        <v>387971</v>
       </c>
       <c r="R19" t="n">
-        <v>6723547</v>
+        <v>6723631</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,12 +2658,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120970920</v>
+        <v>120970927</v>
       </c>
       <c r="B55" t="n">
-        <v>78601</v>
+        <v>78635</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>388053</v>
+        <v>387791</v>
       </c>
       <c r="R55" t="n">
-        <v>6723664</v>
+        <v>6723505</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6444,10 +6444,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120970927</v>
+        <v>120970920</v>
       </c>
       <c r="B57" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6460,21 +6460,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6484,10 +6484,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>387791</v>
+        <v>388053</v>
       </c>
       <c r="R57" t="n">
-        <v>6723505</v>
+        <v>6723664</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -3078,10 +3078,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120970942</v>
+        <v>120970923</v>
       </c>
       <c r="B24" t="n">
-        <v>79642</v>
+        <v>78635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3090,25 +3090,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387010</v>
+        <v>387857</v>
       </c>
       <c r="R24" t="n">
-        <v>6723330</v>
+        <v>6723518</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120976747</v>
+        <v>120976758</v>
       </c>
       <c r="B25" t="n">
-        <v>90662</v>
+        <v>78635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,25 +3192,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387814</v>
+        <v>388026</v>
       </c>
       <c r="R25" t="n">
-        <v>6723543</v>
+        <v>6723646</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120970923</v>
+        <v>120976741</v>
       </c>
       <c r="B26" t="n">
         <v>78635</v>
@@ -3318,14 +3318,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387857</v>
+        <v>387768</v>
       </c>
       <c r="R26" t="n">
-        <v>6723518</v>
+        <v>6723513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,19 +3372,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120976758</v>
+        <v>120976745</v>
       </c>
       <c r="B27" t="n">
         <v>78635</v>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>388026</v>
+        <v>387797</v>
       </c>
       <c r="R27" t="n">
-        <v>6723646</v>
+        <v>6723537</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120976741</v>
+        <v>120976740</v>
       </c>
       <c r="B28" t="n">
-        <v>78635</v>
+        <v>80558</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3502,21 +3502,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387768</v>
+        <v>387671</v>
       </c>
       <c r="R28" t="n">
-        <v>6723513</v>
+        <v>6723531</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120976745</v>
+        <v>120970942</v>
       </c>
       <c r="B29" t="n">
-        <v>78635</v>
+        <v>79642</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3600,38 +3600,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387797</v>
+        <v>387010</v>
       </c>
       <c r="R29" t="n">
-        <v>6723537</v>
+        <v>6723330</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,22 +3678,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120976740</v>
+        <v>120976747</v>
       </c>
       <c r="B30" t="n">
-        <v>80558</v>
+        <v>90662</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3702,25 +3702,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387671</v>
+        <v>387814</v>
       </c>
       <c r="R30" t="n">
-        <v>6723531</v>
+        <v>6723543</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4098,10 +4098,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120976749</v>
+        <v>120976742</v>
       </c>
       <c r="B34" t="n">
-        <v>82385</v>
+        <v>74692</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4110,25 +4110,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387877</v>
+        <v>387783</v>
       </c>
       <c r="R34" t="n">
-        <v>6723565</v>
+        <v>6723518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4200,10 +4200,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120976742</v>
+        <v>120976749</v>
       </c>
       <c r="B35" t="n">
-        <v>74692</v>
+        <v>82385</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4212,25 +4212,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6439</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>387783</v>
+        <v>387877</v>
       </c>
       <c r="R35" t="n">
-        <v>6723518</v>
+        <v>6723565</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -2262,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120970937</v>
+        <v>120970940</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,25 +2274,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>386898</v>
+        <v>387010</v>
       </c>
       <c r="R16" t="n">
-        <v>6723285</v>
+        <v>6723330</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120970939</v>
+        <v>120976743</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>78635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,34 +2380,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>386858</v>
+        <v>387788</v>
       </c>
       <c r="R17" t="n">
-        <v>6723265</v>
+        <v>6723519</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,22 +2454,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120970928</v>
+        <v>120970948</v>
       </c>
       <c r="B18" t="n">
-        <v>82385</v>
+        <v>88024</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2482,21 +2482,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387650</v>
+        <v>387470</v>
       </c>
       <c r="R18" t="n">
-        <v>6723547</v>
+        <v>6723459</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120976755</v>
+        <v>120976740</v>
       </c>
       <c r="B19" t="n">
-        <v>78635</v>
+        <v>80558</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2584,21 +2584,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387971</v>
+        <v>387671</v>
       </c>
       <c r="R19" t="n">
-        <v>6723631</v>
+        <v>6723531</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120976748</v>
+        <v>120970930</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>82385</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2686,31 +2686,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387836</v>
+        <v>387646</v>
       </c>
       <c r="R20" t="n">
         <v>6723530</v>
@@ -2760,22 +2760,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120976727</v>
+        <v>120970922</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>78635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,34 +2788,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386876</v>
+        <v>387956</v>
       </c>
       <c r="R21" t="n">
-        <v>6723260</v>
+        <v>6723630</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,19 +2862,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120976756</v>
+        <v>120970925</v>
       </c>
       <c r="B22" t="n">
         <v>78635</v>
@@ -2910,14 +2910,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387997</v>
+        <v>387824</v>
       </c>
       <c r="R22" t="n">
-        <v>6723622</v>
+        <v>6723508</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2964,22 +2964,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120976738</v>
+        <v>120970942</v>
       </c>
       <c r="B23" t="n">
-        <v>82385</v>
+        <v>79642</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2988,38 +2988,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>387659</v>
+        <v>387010</v>
       </c>
       <c r="R23" t="n">
-        <v>6723515</v>
+        <v>6723330</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,19 +3066,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120970923</v>
+        <v>120970926</v>
       </c>
       <c r="B24" t="n">
         <v>78635</v>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387857</v>
+        <v>387809</v>
       </c>
       <c r="R24" t="n">
-        <v>6723518</v>
+        <v>6723508</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120976758</v>
+        <v>120976726</v>
       </c>
       <c r="B25" t="n">
-        <v>78635</v>
+        <v>82385</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>388026</v>
+        <v>387454</v>
       </c>
       <c r="R25" t="n">
-        <v>6723646</v>
+        <v>6723442</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120976741</v>
+        <v>120976749</v>
       </c>
       <c r="B26" t="n">
-        <v>78635</v>
+        <v>82385</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3298,21 +3298,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387768</v>
+        <v>387877</v>
       </c>
       <c r="R26" t="n">
-        <v>6723513</v>
+        <v>6723565</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120976745</v>
+        <v>120976741</v>
       </c>
       <c r="B27" t="n">
         <v>78635</v>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387797</v>
+        <v>387768</v>
       </c>
       <c r="R27" t="n">
-        <v>6723537</v>
+        <v>6723513</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120976740</v>
+        <v>120976745</v>
       </c>
       <c r="B28" t="n">
-        <v>80558</v>
+        <v>78635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3502,21 +3502,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387671</v>
+        <v>387797</v>
       </c>
       <c r="R28" t="n">
-        <v>6723531</v>
+        <v>6723537</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120970942</v>
+        <v>120970931</v>
       </c>
       <c r="B29" t="n">
-        <v>79642</v>
+        <v>95628</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3600,25 +3600,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387010</v>
+        <v>387533</v>
       </c>
       <c r="R29" t="n">
-        <v>6723330</v>
+        <v>6723413</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120976746</v>
+        <v>120976748</v>
       </c>
       <c r="B31" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387815</v>
+        <v>387836</v>
       </c>
       <c r="R31" t="n">
-        <v>6723536</v>
+        <v>6723530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120970922</v>
+        <v>120970937</v>
       </c>
       <c r="B32" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387956</v>
+        <v>386898</v>
       </c>
       <c r="R32" t="n">
-        <v>6723630</v>
+        <v>6723285</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120976734</v>
+        <v>120970928</v>
       </c>
       <c r="B33" t="n">
-        <v>78338</v>
+        <v>82385</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387161</v>
+        <v>387650</v>
       </c>
       <c r="R33" t="n">
-        <v>6723401</v>
+        <v>6723547</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,22 +4086,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120976742</v>
+        <v>120970943</v>
       </c>
       <c r="B34" t="n">
-        <v>74692</v>
+        <v>79711</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4114,34 +4114,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387783</v>
+        <v>387078</v>
       </c>
       <c r="R34" t="n">
-        <v>6723518</v>
+        <v>6723335</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,22 +4188,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120976749</v>
+        <v>120970939</v>
       </c>
       <c r="B35" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4216,34 +4216,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>387877</v>
+        <v>386858</v>
       </c>
       <c r="R35" t="n">
-        <v>6723565</v>
+        <v>6723265</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,22 +4290,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120970933</v>
+        <v>120970924</v>
       </c>
       <c r="B36" t="n">
-        <v>79642</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4314,25 +4314,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4342,10 +4342,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>387048</v>
+        <v>387816</v>
       </c>
       <c r="R36" t="n">
-        <v>6723350</v>
+        <v>6723527</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4404,10 +4404,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120976731</v>
+        <v>120976746</v>
       </c>
       <c r="B37" t="n">
-        <v>88024</v>
+        <v>78635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4420,21 +4420,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>386893</v>
+        <v>387815</v>
       </c>
       <c r="R37" t="n">
-        <v>6723204</v>
+        <v>6723536</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4506,10 +4506,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120976757</v>
+        <v>120976730</v>
       </c>
       <c r="B38" t="n">
-        <v>78601</v>
+        <v>82385</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>388006</v>
+        <v>386895</v>
       </c>
       <c r="R38" t="n">
-        <v>6723626</v>
+        <v>6723208</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120970926</v>
+        <v>120976760</v>
       </c>
       <c r="B39" t="n">
-        <v>78635</v>
+        <v>95628</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>387809</v>
+        <v>388074</v>
       </c>
       <c r="R39" t="n">
-        <v>6723508</v>
+        <v>6723700</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4698,19 +4698,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120970948</v>
+        <v>120976736</v>
       </c>
       <c r="B40" t="n">
         <v>88024</v>
@@ -4746,14 +4746,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387470</v>
+        <v>387487</v>
       </c>
       <c r="R40" t="n">
-        <v>6723459</v>
+        <v>6723421</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,19 +4800,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120970921</v>
+        <v>120976752</v>
       </c>
       <c r="B41" t="n">
         <v>78635</v>
@@ -4848,11 +4848,11 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387966</v>
+        <v>387969</v>
       </c>
       <c r="R41" t="n">
         <v>6723628</v>
@@ -4902,22 +4902,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120970931</v>
+        <v>120976735</v>
       </c>
       <c r="B42" t="n">
-        <v>95628</v>
+        <v>90662</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4926,38 +4926,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387533</v>
+        <v>387303</v>
       </c>
       <c r="R42" t="n">
-        <v>6723413</v>
+        <v>6723425</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5004,22 +5004,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120976730</v>
+        <v>120976754</v>
       </c>
       <c r="B43" t="n">
-        <v>82385</v>
+        <v>88024</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>386895</v>
+        <v>387963</v>
       </c>
       <c r="R43" t="n">
-        <v>6723208</v>
+        <v>6723633</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5118,10 +5118,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120970936</v>
+        <v>120970945</v>
       </c>
       <c r="B44" t="n">
-        <v>78601</v>
+        <v>90662</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5130,25 +5130,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>386940</v>
+        <v>387254</v>
       </c>
       <c r="R44" t="n">
-        <v>6723292</v>
+        <v>6723421</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120976744</v>
+        <v>120970923</v>
       </c>
       <c r="B45" t="n">
-        <v>78601</v>
+        <v>78635</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5236,34 +5236,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387795</v>
+        <v>387857</v>
       </c>
       <c r="R45" t="n">
-        <v>6723523</v>
+        <v>6723518</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5310,12 +5310,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5424,10 +5424,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120976754</v>
+        <v>120976738</v>
       </c>
       <c r="B47" t="n">
-        <v>88024</v>
+        <v>82385</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,21 +5440,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387963</v>
+        <v>387659</v>
       </c>
       <c r="R47" t="n">
-        <v>6723633</v>
+        <v>6723515</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120970925</v>
+        <v>120970927</v>
       </c>
       <c r="B48" t="n">
         <v>78635</v>
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387824</v>
+        <v>387791</v>
       </c>
       <c r="R48" t="n">
-        <v>6723508</v>
+        <v>6723505</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5628,10 +5628,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120970943</v>
+        <v>120976751</v>
       </c>
       <c r="B49" t="n">
-        <v>79711</v>
+        <v>79219</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5640,38 +5640,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387078</v>
+        <v>387955</v>
       </c>
       <c r="R49" t="n">
-        <v>6723335</v>
+        <v>6723604</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5718,22 +5718,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120970934</v>
+        <v>120976756</v>
       </c>
       <c r="B50" t="n">
-        <v>90662</v>
+        <v>78635</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5742,38 +5742,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>387036</v>
+        <v>387997</v>
       </c>
       <c r="R50" t="n">
-        <v>6723319</v>
+        <v>6723622</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5820,22 +5820,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120970945</v>
+        <v>120976758</v>
       </c>
       <c r="B51" t="n">
-        <v>90662</v>
+        <v>78635</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5844,38 +5844,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>387254</v>
+        <v>388026</v>
       </c>
       <c r="R51" t="n">
-        <v>6723421</v>
+        <v>6723646</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5922,22 +5922,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120976728</v>
+        <v>120970921</v>
       </c>
       <c r="B52" t="n">
-        <v>88024</v>
+        <v>78635</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5950,34 +5950,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>386791</v>
+        <v>387966</v>
       </c>
       <c r="R52" t="n">
-        <v>6723204</v>
+        <v>6723628</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6024,19 +6024,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120976743</v>
+        <v>120976755</v>
       </c>
       <c r="B53" t="n">
         <v>78635</v>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387788</v>
+        <v>387971</v>
       </c>
       <c r="R53" t="n">
-        <v>6723519</v>
+        <v>6723631</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120976760</v>
+        <v>120976727</v>
       </c>
       <c r="B54" t="n">
-        <v>95628</v>
+        <v>78601</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6154,21 +6154,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>388074</v>
+        <v>386876</v>
       </c>
       <c r="R54" t="n">
-        <v>6723700</v>
+        <v>6723260</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120970927</v>
+        <v>120976744</v>
       </c>
       <c r="B55" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6256,34 +6256,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387791</v>
+        <v>387795</v>
       </c>
       <c r="R55" t="n">
-        <v>6723505</v>
+        <v>6723523</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6330,22 +6330,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120976752</v>
+        <v>120970936</v>
       </c>
       <c r="B56" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6358,34 +6358,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387969</v>
+        <v>386940</v>
       </c>
       <c r="R56" t="n">
-        <v>6723628</v>
+        <v>6723292</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6432,12 +6432,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6546,10 +6546,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120976751</v>
+        <v>120976734</v>
       </c>
       <c r="B58" t="n">
-        <v>79219</v>
+        <v>78338</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6562,21 +6562,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>387955</v>
+        <v>387161</v>
       </c>
       <c r="R58" t="n">
-        <v>6723604</v>
+        <v>6723401</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6648,10 +6648,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120970930</v>
+        <v>120976742</v>
       </c>
       <c r="B59" t="n">
-        <v>82385</v>
+        <v>74692</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6660,38 +6660,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>6439</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>387646</v>
+        <v>387783</v>
       </c>
       <c r="R59" t="n">
-        <v>6723530</v>
+        <v>6723518</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6738,22 +6738,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120976726</v>
+        <v>120970934</v>
       </c>
       <c r="B60" t="n">
-        <v>82385</v>
+        <v>90662</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6762,38 +6762,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>387454</v>
+        <v>387036</v>
       </c>
       <c r="R60" t="n">
-        <v>6723442</v>
+        <v>6723319</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6840,22 +6840,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120970940</v>
+        <v>120976757</v>
       </c>
       <c r="B61" t="n">
-        <v>79711</v>
+        <v>78601</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6864,38 +6864,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>387010</v>
+        <v>388006</v>
       </c>
       <c r="R61" t="n">
-        <v>6723330</v>
+        <v>6723626</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6942,22 +6942,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120976735</v>
+        <v>120976728</v>
       </c>
       <c r="B62" t="n">
-        <v>90662</v>
+        <v>88024</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6966,25 +6966,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6994,10 +6994,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>387303</v>
+        <v>386791</v>
       </c>
       <c r="R62" t="n">
-        <v>6723425</v>
+        <v>6723204</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7056,10 +7056,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120970924</v>
+        <v>120970946</v>
       </c>
       <c r="B63" t="n">
-        <v>78601</v>
+        <v>88024</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7072,21 +7072,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>387816</v>
+        <v>387338</v>
       </c>
       <c r="R63" t="n">
-        <v>6723527</v>
+        <v>6723431</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7158,10 +7158,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120970946</v>
+        <v>120970933</v>
       </c>
       <c r="B64" t="n">
-        <v>88024</v>
+        <v>79642</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7170,25 +7170,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>387338</v>
+        <v>387048</v>
       </c>
       <c r="R64" t="n">
-        <v>6723431</v>
+        <v>6723350</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7260,7 +7260,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120976736</v>
+        <v>120976731</v>
       </c>
       <c r="B65" t="n">
         <v>88024</v>
@@ -7300,10 +7300,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>387487</v>
+        <v>386893</v>
       </c>
       <c r="R65" t="n">
-        <v>6723421</v>
+        <v>6723204</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -3282,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120976749</v>
+        <v>120976747</v>
       </c>
       <c r="B26" t="n">
-        <v>82385</v>
+        <v>90662</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3294,25 +3294,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387877</v>
+        <v>387814</v>
       </c>
       <c r="R26" t="n">
-        <v>6723565</v>
+        <v>6723543</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120976741</v>
+        <v>120976748</v>
       </c>
       <c r="B27" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3400,21 +3400,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387768</v>
+        <v>387836</v>
       </c>
       <c r="R27" t="n">
-        <v>6723513</v>
+        <v>6723530</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120976745</v>
+        <v>120970937</v>
       </c>
       <c r="B28" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3502,34 +3502,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387797</v>
+        <v>386898</v>
       </c>
       <c r="R28" t="n">
-        <v>6723537</v>
+        <v>6723285</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3576,22 +3576,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120970931</v>
+        <v>120976749</v>
       </c>
       <c r="B29" t="n">
-        <v>95628</v>
+        <v>82385</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3604,34 +3604,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387533</v>
+        <v>387877</v>
       </c>
       <c r="R29" t="n">
-        <v>6723413</v>
+        <v>6723565</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3678,22 +3678,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120976747</v>
+        <v>120976741</v>
       </c>
       <c r="B30" t="n">
-        <v>90662</v>
+        <v>78635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3702,25 +3702,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387814</v>
+        <v>387768</v>
       </c>
       <c r="R30" t="n">
-        <v>6723543</v>
+        <v>6723513</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120976748</v>
+        <v>120976745</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>78635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387836</v>
+        <v>387797</v>
       </c>
       <c r="R31" t="n">
-        <v>6723530</v>
+        <v>6723537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120970937</v>
+        <v>120970931</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>95628</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3910,21 +3910,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3934,10 +3934,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386898</v>
+        <v>387533</v>
       </c>
       <c r="R32" t="n">
-        <v>6723285</v>
+        <v>6723413</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5730,10 +5730,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120976756</v>
+        <v>120976727</v>
       </c>
       <c r="B50" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5746,21 +5746,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>387997</v>
+        <v>386876</v>
       </c>
       <c r="R50" t="n">
-        <v>6723622</v>
+        <v>6723260</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5832,10 +5832,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120976758</v>
+        <v>120976744</v>
       </c>
       <c r="B51" t="n">
-        <v>78635</v>
+        <v>78601</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>388026</v>
+        <v>387795</v>
       </c>
       <c r="R51" t="n">
-        <v>6723646</v>
+        <v>6723523</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5934,7 +5934,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120970921</v>
+        <v>120976756</v>
       </c>
       <c r="B52" t="n">
         <v>78635</v>
@@ -5970,14 +5970,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>387966</v>
+        <v>387997</v>
       </c>
       <c r="R52" t="n">
-        <v>6723628</v>
+        <v>6723622</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6024,19 +6024,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120976755</v>
+        <v>120976758</v>
       </c>
       <c r="B53" t="n">
         <v>78635</v>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387971</v>
+        <v>388026</v>
       </c>
       <c r="R53" t="n">
-        <v>6723631</v>
+        <v>6723646</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120976727</v>
+        <v>120970921</v>
       </c>
       <c r="B54" t="n">
-        <v>78601</v>
+        <v>78635</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6154,34 +6154,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>386876</v>
+        <v>387966</v>
       </c>
       <c r="R54" t="n">
-        <v>6723260</v>
+        <v>6723628</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6228,22 +6228,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120976744</v>
+        <v>120976755</v>
       </c>
       <c r="B55" t="n">
-        <v>78601</v>
+        <v>78635</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387795</v>
+        <v>387971</v>
       </c>
       <c r="R55" t="n">
-        <v>6723523</v>
+        <v>6723631</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6750,10 +6750,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120970934</v>
+        <v>120976757</v>
       </c>
       <c r="B60" t="n">
-        <v>90662</v>
+        <v>78601</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6762,38 +6762,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>387036</v>
+        <v>388006</v>
       </c>
       <c r="R60" t="n">
-        <v>6723319</v>
+        <v>6723626</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6840,22 +6840,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120976757</v>
+        <v>120970933</v>
       </c>
       <c r="B61" t="n">
-        <v>78601</v>
+        <v>79642</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6864,38 +6864,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>388006</v>
+        <v>387048</v>
       </c>
       <c r="R61" t="n">
-        <v>6723626</v>
+        <v>6723350</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6942,22 +6942,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120976728</v>
+        <v>120970934</v>
       </c>
       <c r="B62" t="n">
-        <v>88024</v>
+        <v>90662</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6966,38 +6966,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>386791</v>
+        <v>387036</v>
       </c>
       <c r="R62" t="n">
-        <v>6723204</v>
+        <v>6723319</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7044,19 +7044,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120970946</v>
+        <v>120976728</v>
       </c>
       <c r="B63" t="n">
         <v>88024</v>
@@ -7092,14 +7092,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>387338</v>
+        <v>386791</v>
       </c>
       <c r="R63" t="n">
-        <v>6723431</v>
+        <v>6723204</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7146,22 +7146,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120970933</v>
+        <v>120970946</v>
       </c>
       <c r="B64" t="n">
-        <v>79642</v>
+        <v>88024</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7170,25 +7170,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>510</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>387048</v>
+        <v>387338</v>
       </c>
       <c r="R64" t="n">
-        <v>6723350</v>
+        <v>6723431</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -2262,10 +2262,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120970940</v>
+        <v>120976760</v>
       </c>
       <c r="B16" t="n">
-        <v>79711</v>
+        <v>95641</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,38 +2274,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>387010</v>
+        <v>388074</v>
       </c>
       <c r="R16" t="n">
-        <v>6723330</v>
+        <v>6723700</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,22 +2352,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120976743</v>
+        <v>120970943</v>
       </c>
       <c r="B17" t="n">
-        <v>78635</v>
+        <v>79714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,38 +2376,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387788</v>
+        <v>387078</v>
       </c>
       <c r="R17" t="n">
-        <v>6723519</v>
+        <v>6723335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,22 +2454,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120970948</v>
+        <v>120970920</v>
       </c>
       <c r="B18" t="n">
-        <v>88024</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2482,21 +2482,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387470</v>
+        <v>388053</v>
       </c>
       <c r="R18" t="n">
-        <v>6723459</v>
+        <v>6723664</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120976740</v>
+        <v>120970948</v>
       </c>
       <c r="B19" t="n">
-        <v>80558</v>
+        <v>88031</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2584,34 +2584,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387671</v>
+        <v>387470</v>
       </c>
       <c r="R19" t="n">
-        <v>6723531</v>
+        <v>6723459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,12 +2658,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2673,7 +2673,7 @@
         <v>120970930</v>
       </c>
       <c r="B20" t="n">
-        <v>82385</v>
+        <v>82388</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120970922</v>
+        <v>120970939</v>
       </c>
       <c r="B21" t="n">
-        <v>78635</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>387956</v>
+        <v>386858</v>
       </c>
       <c r="R21" t="n">
-        <v>6723630</v>
+        <v>6723265</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120970925</v>
+        <v>120970933</v>
       </c>
       <c r="B22" t="n">
-        <v>78635</v>
+        <v>79645</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2886,25 +2886,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387824</v>
+        <v>387048</v>
       </c>
       <c r="R22" t="n">
-        <v>6723508</v>
+        <v>6723350</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2976,10 +2976,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120970942</v>
+        <v>120970928</v>
       </c>
       <c r="B23" t="n">
-        <v>79642</v>
+        <v>82388</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2988,25 +2988,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>387010</v>
+        <v>387650</v>
       </c>
       <c r="R23" t="n">
-        <v>6723330</v>
+        <v>6723547</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120970926</v>
+        <v>120976756</v>
       </c>
       <c r="B24" t="n">
-        <v>78635</v>
+        <v>78638</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3114,14 +3114,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387809</v>
+        <v>387997</v>
       </c>
       <c r="R24" t="n">
-        <v>6723508</v>
+        <v>6723622</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3168,22 +3168,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120976726</v>
+        <v>120976727</v>
       </c>
       <c r="B25" t="n">
-        <v>82385</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>387454</v>
+        <v>386876</v>
       </c>
       <c r="R25" t="n">
-        <v>6723442</v>
+        <v>6723260</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120976747</v>
+        <v>120976752</v>
       </c>
       <c r="B26" t="n">
-        <v>90662</v>
+        <v>78638</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3294,25 +3294,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387814</v>
+        <v>387969</v>
       </c>
       <c r="R26" t="n">
-        <v>6723543</v>
+        <v>6723628</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120976748</v>
+        <v>120970924</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3420,14 +3420,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387836</v>
+        <v>387816</v>
       </c>
       <c r="R27" t="n">
-        <v>6723530</v>
+        <v>6723527</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3474,22 +3474,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120970937</v>
+        <v>120976740</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>80561</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3502,34 +3502,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>386898</v>
+        <v>387671</v>
       </c>
       <c r="R28" t="n">
-        <v>6723285</v>
+        <v>6723531</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3576,22 +3576,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120976749</v>
+        <v>120976747</v>
       </c>
       <c r="B29" t="n">
-        <v>82385</v>
+        <v>90674</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3600,25 +3600,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3628,10 +3628,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387877</v>
+        <v>387814</v>
       </c>
       <c r="R29" t="n">
-        <v>6723565</v>
+        <v>6723543</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,10 +3690,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120976741</v>
+        <v>120976759</v>
       </c>
       <c r="B30" t="n">
-        <v>78635</v>
+        <v>78604</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3706,21 +3706,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>387768</v>
+        <v>388030</v>
       </c>
       <c r="R30" t="n">
-        <v>6723513</v>
+        <v>6723650</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3792,10 +3792,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120976745</v>
+        <v>120976738</v>
       </c>
       <c r="B31" t="n">
-        <v>78635</v>
+        <v>82388</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3808,21 +3808,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387797</v>
+        <v>387659</v>
       </c>
       <c r="R31" t="n">
-        <v>6723537</v>
+        <v>6723515</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120970931</v>
+        <v>120976730</v>
       </c>
       <c r="B32" t="n">
-        <v>95628</v>
+        <v>82388</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3910,34 +3910,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>387533</v>
+        <v>386895</v>
       </c>
       <c r="R32" t="n">
-        <v>6723413</v>
+        <v>6723208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3984,22 +3984,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120970928</v>
+        <v>120976751</v>
       </c>
       <c r="B33" t="n">
-        <v>82385</v>
+        <v>79222</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387650</v>
+        <v>387955</v>
       </c>
       <c r="R33" t="n">
-        <v>6723547</v>
+        <v>6723604</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4086,22 +4086,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120970943</v>
+        <v>120970923</v>
       </c>
       <c r="B34" t="n">
-        <v>79711</v>
+        <v>78638</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4110,25 +4110,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387078</v>
+        <v>387857</v>
       </c>
       <c r="R34" t="n">
-        <v>6723335</v>
+        <v>6723518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4200,10 +4200,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120970939</v>
+        <v>120976744</v>
       </c>
       <c r="B35" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4236,14 +4236,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>386858</v>
+        <v>387795</v>
       </c>
       <c r="R35" t="n">
-        <v>6723265</v>
+        <v>6723523</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,22 +4290,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120970924</v>
+        <v>120976757</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4338,14 +4338,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>387816</v>
+        <v>388006</v>
       </c>
       <c r="R36" t="n">
-        <v>6723527</v>
+        <v>6723626</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4392,22 +4392,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120976746</v>
+        <v>120970922</v>
       </c>
       <c r="B37" t="n">
-        <v>78635</v>
+        <v>78638</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4440,14 +4440,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387815</v>
+        <v>387956</v>
       </c>
       <c r="R37" t="n">
-        <v>6723536</v>
+        <v>6723630</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4494,22 +4494,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120976730</v>
+        <v>120976743</v>
       </c>
       <c r="B38" t="n">
-        <v>82385</v>
+        <v>78638</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4522,21 +4522,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>386895</v>
+        <v>387788</v>
       </c>
       <c r="R38" t="n">
-        <v>6723208</v>
+        <v>6723519</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120976760</v>
+        <v>120970937</v>
       </c>
       <c r="B39" t="n">
-        <v>95628</v>
+        <v>78604</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4624,34 +4624,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>388074</v>
+        <v>386898</v>
       </c>
       <c r="R39" t="n">
-        <v>6723700</v>
+        <v>6723285</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4698,22 +4698,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120976736</v>
+        <v>120970934</v>
       </c>
       <c r="B40" t="n">
-        <v>88024</v>
+        <v>90674</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4722,38 +4722,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387487</v>
+        <v>387036</v>
       </c>
       <c r="R40" t="n">
-        <v>6723421</v>
+        <v>6723319</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4800,22 +4800,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120976752</v>
+        <v>120976746</v>
       </c>
       <c r="B41" t="n">
-        <v>78635</v>
+        <v>78638</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387969</v>
+        <v>387815</v>
       </c>
       <c r="R41" t="n">
-        <v>6723628</v>
+        <v>6723536</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4914,10 +4914,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120976735</v>
+        <v>120970921</v>
       </c>
       <c r="B42" t="n">
-        <v>90662</v>
+        <v>78638</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4926,38 +4926,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387303</v>
+        <v>387966</v>
       </c>
       <c r="R42" t="n">
-        <v>6723425</v>
+        <v>6723628</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5004,22 +5004,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120976754</v>
+        <v>120976726</v>
       </c>
       <c r="B43" t="n">
-        <v>88024</v>
+        <v>82388</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387963</v>
+        <v>387454</v>
       </c>
       <c r="R43" t="n">
-        <v>6723633</v>
+        <v>6723442</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5118,10 +5118,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120970945</v>
+        <v>120976745</v>
       </c>
       <c r="B44" t="n">
-        <v>90662</v>
+        <v>78638</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5130,38 +5130,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387254</v>
+        <v>387797</v>
       </c>
       <c r="R44" t="n">
-        <v>6723421</v>
+        <v>6723537</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5208,22 +5208,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120970923</v>
+        <v>120970931</v>
       </c>
       <c r="B45" t="n">
-        <v>78635</v>
+        <v>95641</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5236,21 +5236,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387857</v>
+        <v>387533</v>
       </c>
       <c r="R45" t="n">
-        <v>6723518</v>
+        <v>6723413</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120976759</v>
+        <v>120970936</v>
       </c>
       <c r="B46" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5358,14 +5358,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>388030</v>
+        <v>386940</v>
       </c>
       <c r="R46" t="n">
-        <v>6723650</v>
+        <v>6723292</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5412,22 +5412,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120976738</v>
+        <v>120976734</v>
       </c>
       <c r="B47" t="n">
-        <v>82385</v>
+        <v>78341</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5440,21 +5440,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387659</v>
+        <v>387161</v>
       </c>
       <c r="R47" t="n">
-        <v>6723515</v>
+        <v>6723401</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5526,10 +5526,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120970927</v>
+        <v>120970942</v>
       </c>
       <c r="B48" t="n">
-        <v>78635</v>
+        <v>79645</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5538,25 +5538,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387791</v>
+        <v>387010</v>
       </c>
       <c r="R48" t="n">
-        <v>6723505</v>
+        <v>6723330</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5628,10 +5628,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120976751</v>
+        <v>120976754</v>
       </c>
       <c r="B49" t="n">
-        <v>79219</v>
+        <v>88031</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5644,21 +5644,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5668,10 +5668,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387955</v>
+        <v>387963</v>
       </c>
       <c r="R49" t="n">
-        <v>6723604</v>
+        <v>6723633</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5730,10 +5730,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120976727</v>
+        <v>120976742</v>
       </c>
       <c r="B50" t="n">
-        <v>78601</v>
+        <v>74694</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5742,25 +5742,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>386876</v>
+        <v>387783</v>
       </c>
       <c r="R50" t="n">
-        <v>6723260</v>
+        <v>6723518</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5832,10 +5832,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120976744</v>
+        <v>120976731</v>
       </c>
       <c r="B51" t="n">
-        <v>78601</v>
+        <v>88031</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>387795</v>
+        <v>386893</v>
       </c>
       <c r="R51" t="n">
-        <v>6723523</v>
+        <v>6723204</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5934,10 +5934,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120976756</v>
+        <v>120976741</v>
       </c>
       <c r="B52" t="n">
-        <v>78635</v>
+        <v>78638</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5974,10 +5974,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>387997</v>
+        <v>387768</v>
       </c>
       <c r="R52" t="n">
-        <v>6723622</v>
+        <v>6723513</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6036,10 +6036,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120976758</v>
+        <v>120976736</v>
       </c>
       <c r="B53" t="n">
-        <v>78635</v>
+        <v>88031</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6052,21 +6052,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>388026</v>
+        <v>387487</v>
       </c>
       <c r="R53" t="n">
-        <v>6723646</v>
+        <v>6723421</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120970921</v>
+        <v>120970927</v>
       </c>
       <c r="B54" t="n">
-        <v>78635</v>
+        <v>78638</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387966</v>
+        <v>387791</v>
       </c>
       <c r="R54" t="n">
-        <v>6723628</v>
+        <v>6723505</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6240,10 +6240,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120976755</v>
+        <v>120976748</v>
       </c>
       <c r="B55" t="n">
-        <v>78635</v>
+        <v>78604</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387971</v>
+        <v>387836</v>
       </c>
       <c r="R55" t="n">
-        <v>6723631</v>
+        <v>6723530</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6342,10 +6342,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120970936</v>
+        <v>120970925</v>
       </c>
       <c r="B56" t="n">
-        <v>78601</v>
+        <v>78638</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6358,21 +6358,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>386940</v>
+        <v>387824</v>
       </c>
       <c r="R56" t="n">
-        <v>6723292</v>
+        <v>6723508</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6444,10 +6444,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120970920</v>
+        <v>120976728</v>
       </c>
       <c r="B57" t="n">
-        <v>78601</v>
+        <v>88031</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6460,34 +6460,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>388053</v>
+        <v>386791</v>
       </c>
       <c r="R57" t="n">
-        <v>6723664</v>
+        <v>6723204</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6534,22 +6534,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120976734</v>
+        <v>120976749</v>
       </c>
       <c r="B58" t="n">
-        <v>78338</v>
+        <v>82388</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6562,21 +6562,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>387161</v>
+        <v>387877</v>
       </c>
       <c r="R58" t="n">
-        <v>6723401</v>
+        <v>6723565</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6648,10 +6648,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120976742</v>
+        <v>120970946</v>
       </c>
       <c r="B59" t="n">
-        <v>74692</v>
+        <v>88031</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6660,38 +6660,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6439</v>
+        <v>510</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>387783</v>
+        <v>387338</v>
       </c>
       <c r="R59" t="n">
-        <v>6723518</v>
+        <v>6723431</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6738,22 +6738,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120976757</v>
+        <v>120976758</v>
       </c>
       <c r="B60" t="n">
-        <v>78601</v>
+        <v>78638</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6766,21 +6766,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6790,10 +6790,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>388006</v>
+        <v>388026</v>
       </c>
       <c r="R60" t="n">
-        <v>6723626</v>
+        <v>6723646</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6852,10 +6852,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120970933</v>
+        <v>120976755</v>
       </c>
       <c r="B61" t="n">
-        <v>79642</v>
+        <v>78638</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6864,38 +6864,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>387048</v>
+        <v>387971</v>
       </c>
       <c r="R61" t="n">
-        <v>6723350</v>
+        <v>6723631</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6942,22 +6942,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120970934</v>
+        <v>120976735</v>
       </c>
       <c r="B62" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6990,14 +6990,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>387036</v>
+        <v>387303</v>
       </c>
       <c r="R62" t="n">
-        <v>6723319</v>
+        <v>6723425</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7044,22 +7044,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120976728</v>
+        <v>120970926</v>
       </c>
       <c r="B63" t="n">
-        <v>88024</v>
+        <v>78638</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7072,34 +7072,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>386791</v>
+        <v>387809</v>
       </c>
       <c r="R63" t="n">
-        <v>6723204</v>
+        <v>6723508</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7146,22 +7146,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120970946</v>
+        <v>120970940</v>
       </c>
       <c r="B64" t="n">
-        <v>88024</v>
+        <v>79714</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7170,25 +7170,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>387338</v>
+        <v>387010</v>
       </c>
       <c r="R64" t="n">
-        <v>6723431</v>
+        <v>6723330</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7260,10 +7260,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120976731</v>
+        <v>120970945</v>
       </c>
       <c r="B65" t="n">
-        <v>88024</v>
+        <v>90674</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7272,38 +7272,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>386893</v>
+        <v>387254</v>
       </c>
       <c r="R65" t="n">
-        <v>6723204</v>
+        <v>6723421</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7350,12 +7350,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7360,6 +7360,1653 @@
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>121672246</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79696</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>387932</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6723626</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>121672245</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79655</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>387056</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6723350</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>121672239</v>
+      </c>
+      <c r="B68" t="n">
+        <v>90725</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>387391</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6723451</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>121672247</v>
+      </c>
+      <c r="B69" t="n">
+        <v>90690</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>387273</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6723412</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>121672249</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79695</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>386886</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6723261</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>121672243</v>
+      </c>
+      <c r="B71" t="n">
+        <v>90743</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>388056</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6723670</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>121672254</v>
+      </c>
+      <c r="B72" t="n">
+        <v>90725</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>387774</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6723594</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>121672248</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79232</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>387664</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6723537</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>121672250</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78648</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>185</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>386886</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6723261</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>121672240</v>
+      </c>
+      <c r="B75" t="n">
+        <v>90743</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>387775</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6723585</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>121672251</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79695</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>387205</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6723389</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>121672242</v>
+      </c>
+      <c r="B77" t="n">
+        <v>74712</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>308</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>387833</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6723529</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>121672244</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78648</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>185</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>387777</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6723536</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>121672241</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79695</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>386889</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6723271</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På död björk.</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>121672255</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79655</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>387034</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6723332</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>121672252</v>
+      </c>
+      <c r="B81" t="n">
+        <v>90690</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>386906</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6723248</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672246</v>
+        <v>121672250</v>
       </c>
       <c r="B66" t="n">
-        <v>79696</v>
+        <v>78650</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7378,21 +7378,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387932</v>
+        <v>386886</v>
       </c>
       <c r="R66" t="n">
-        <v>6723626</v>
+        <v>6723261</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7438,6 +7438,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7464,10 +7469,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672245</v>
+        <v>121672246</v>
       </c>
       <c r="B67" t="n">
-        <v>79655</v>
+        <v>79698</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7476,25 +7481,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7509,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387056</v>
+        <v>387932</v>
       </c>
       <c r="R67" t="n">
-        <v>6723350</v>
+        <v>6723626</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7566,10 +7571,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672239</v>
+        <v>121672244</v>
       </c>
       <c r="B68" t="n">
-        <v>90725</v>
+        <v>78650</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7582,21 +7587,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7606,10 +7611,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387391</v>
+        <v>387777</v>
       </c>
       <c r="R68" t="n">
-        <v>6723451</v>
+        <v>6723536</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7668,10 +7673,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672247</v>
+        <v>121672251</v>
       </c>
       <c r="B69" t="n">
-        <v>90690</v>
+        <v>79697</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7680,25 +7685,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7708,10 +7713,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>387273</v>
+        <v>387205</v>
       </c>
       <c r="R69" t="n">
-        <v>6723412</v>
+        <v>6723389</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7770,10 +7775,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121672249</v>
+        <v>121672255</v>
       </c>
       <c r="B70" t="n">
-        <v>79695</v>
+        <v>79657</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7782,25 +7787,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7810,10 +7815,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>386886</v>
+        <v>387034</v>
       </c>
       <c r="R70" t="n">
-        <v>6723261</v>
+        <v>6723332</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7846,11 +7851,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7877,10 +7877,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672243</v>
+        <v>121672239</v>
       </c>
       <c r="B71" t="n">
-        <v>90743</v>
+        <v>90728</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7893,21 +7893,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>388056</v>
+        <v>387391</v>
       </c>
       <c r="R71" t="n">
-        <v>6723670</v>
+        <v>6723451</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7979,10 +7979,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672254</v>
+        <v>121672243</v>
       </c>
       <c r="B72" t="n">
-        <v>90725</v>
+        <v>90746</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7995,21 +7995,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387774</v>
+        <v>388056</v>
       </c>
       <c r="R72" t="n">
-        <v>6723594</v>
+        <v>6723670</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8084,7 +8084,7 @@
         <v>121672248</v>
       </c>
       <c r="B73" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8183,10 +8183,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672250</v>
+        <v>121672245</v>
       </c>
       <c r="B74" t="n">
-        <v>78648</v>
+        <v>79657</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8195,25 +8195,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8223,10 +8223,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>386886</v>
+        <v>387056</v>
       </c>
       <c r="R74" t="n">
-        <v>6723261</v>
+        <v>6723350</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8259,11 +8259,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8290,10 +8285,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672240</v>
+        <v>121672247</v>
       </c>
       <c r="B75" t="n">
-        <v>90743</v>
+        <v>90693</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8302,25 +8297,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8330,10 +8325,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387775</v>
+        <v>387273</v>
       </c>
       <c r="R75" t="n">
-        <v>6723585</v>
+        <v>6723412</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8392,10 +8387,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672251</v>
+        <v>121672252</v>
       </c>
       <c r="B76" t="n">
-        <v>79695</v>
+        <v>90693</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8404,25 +8399,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8432,10 +8427,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387205</v>
+        <v>386906</v>
       </c>
       <c r="R76" t="n">
-        <v>6723389</v>
+        <v>6723248</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8494,10 +8489,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672242</v>
+        <v>121672249</v>
       </c>
       <c r="B77" t="n">
-        <v>74712</v>
+        <v>79697</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8510,21 +8505,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8534,10 +8529,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387833</v>
+        <v>386886</v>
       </c>
       <c r="R77" t="n">
-        <v>6723529</v>
+        <v>6723261</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,6 +8565,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8596,10 +8596,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672244</v>
+        <v>121672254</v>
       </c>
       <c r="B78" t="n">
-        <v>78648</v>
+        <v>90728</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8612,21 +8612,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8636,10 +8636,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>387777</v>
+        <v>387774</v>
       </c>
       <c r="R78" t="n">
-        <v>6723536</v>
+        <v>6723594</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8698,10 +8698,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672241</v>
+        <v>121672242</v>
       </c>
       <c r="B79" t="n">
-        <v>79695</v>
+        <v>74714</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8714,21 +8714,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>386889</v>
+        <v>387833</v>
       </c>
       <c r="R79" t="n">
-        <v>6723271</v>
+        <v>6723529</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8774,11 +8774,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8805,10 +8800,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121672255</v>
+        <v>121672240</v>
       </c>
       <c r="B80" t="n">
-        <v>79655</v>
+        <v>90746</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8817,25 +8812,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8845,10 +8840,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>387034</v>
+        <v>387775</v>
       </c>
       <c r="R80" t="n">
-        <v>6723332</v>
+        <v>6723585</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8907,10 +8902,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672252</v>
+        <v>121672241</v>
       </c>
       <c r="B81" t="n">
-        <v>90690</v>
+        <v>79697</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8919,25 +8914,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8947,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>386906</v>
+        <v>386889</v>
       </c>
       <c r="R81" t="n">
-        <v>6723248</v>
+        <v>6723271</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8983,6 +8978,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7571,10 +7571,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672244</v>
+        <v>121672251</v>
       </c>
       <c r="B68" t="n">
-        <v>78650</v>
+        <v>79697</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7587,21 +7587,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7611,10 +7611,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387777</v>
+        <v>387205</v>
       </c>
       <c r="R68" t="n">
-        <v>6723536</v>
+        <v>6723389</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7673,10 +7673,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672251</v>
+        <v>121672244</v>
       </c>
       <c r="B69" t="n">
-        <v>79697</v>
+        <v>78650</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7689,21 +7689,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>387205</v>
+        <v>387777</v>
       </c>
       <c r="R69" t="n">
-        <v>6723389</v>
+        <v>6723536</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672241</v>
+        <v>121672245</v>
       </c>
       <c r="B66" t="n">
-        <v>79697</v>
+        <v>79657</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7374,25 +7374,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>386889</v>
+        <v>387056</v>
       </c>
       <c r="R66" t="n">
-        <v>6723271</v>
+        <v>6723350</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7438,11 +7438,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7571,10 +7566,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672246</v>
+        <v>121672244</v>
       </c>
       <c r="B68" t="n">
-        <v>79698</v>
+        <v>78650</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7587,21 +7582,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7611,10 +7606,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387932</v>
+        <v>387777</v>
       </c>
       <c r="R68" t="n">
-        <v>6723626</v>
+        <v>6723536</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7673,10 +7668,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672249</v>
+        <v>121672239</v>
       </c>
       <c r="B69" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7689,21 +7684,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7713,10 +7708,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>386886</v>
+        <v>387391</v>
       </c>
       <c r="R69" t="n">
-        <v>6723261</v>
+        <v>6723451</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7749,11 +7744,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7780,10 +7770,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121672240</v>
+        <v>121672242</v>
       </c>
       <c r="B70" t="n">
-        <v>90746</v>
+        <v>74714</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7796,21 +7786,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7820,10 +7810,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>387775</v>
+        <v>387833</v>
       </c>
       <c r="R70" t="n">
-        <v>6723585</v>
+        <v>6723529</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7882,10 +7872,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672242</v>
+        <v>121672248</v>
       </c>
       <c r="B71" t="n">
-        <v>74714</v>
+        <v>79234</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7898,21 +7888,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7922,10 +7912,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387833</v>
+        <v>387664</v>
       </c>
       <c r="R71" t="n">
-        <v>6723529</v>
+        <v>6723537</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7984,10 +7974,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672251</v>
+        <v>121672240</v>
       </c>
       <c r="B72" t="n">
-        <v>79697</v>
+        <v>90746</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8000,21 +7990,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8024,10 +8014,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387205</v>
+        <v>387775</v>
       </c>
       <c r="R72" t="n">
-        <v>6723389</v>
+        <v>6723585</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8086,10 +8076,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121672250</v>
+        <v>121672241</v>
       </c>
       <c r="B73" t="n">
-        <v>78650</v>
+        <v>79697</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8102,21 +8092,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8126,10 +8116,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>386886</v>
+        <v>386889</v>
       </c>
       <c r="R73" t="n">
-        <v>6723261</v>
+        <v>6723271</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8166,7 +8156,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På björk.</t>
+          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8193,10 +8183,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672244</v>
+        <v>121672249</v>
       </c>
       <c r="B74" t="n">
-        <v>78650</v>
+        <v>79697</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8209,21 +8199,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8233,10 +8223,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387777</v>
+        <v>386886</v>
       </c>
       <c r="R74" t="n">
-        <v>6723536</v>
+        <v>6723261</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8269,6 +8259,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8295,10 +8290,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672254</v>
+        <v>121672243</v>
       </c>
       <c r="B75" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8311,21 +8306,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8335,10 +8330,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387774</v>
+        <v>388056</v>
       </c>
       <c r="R75" t="n">
-        <v>6723594</v>
+        <v>6723670</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8397,10 +8392,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672239</v>
+        <v>121672246</v>
       </c>
       <c r="B76" t="n">
-        <v>90728</v>
+        <v>79698</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8413,21 +8408,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8437,10 +8432,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387391</v>
+        <v>387932</v>
       </c>
       <c r="R76" t="n">
-        <v>6723451</v>
+        <v>6723626</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8499,10 +8494,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672245</v>
+        <v>121672252</v>
       </c>
       <c r="B77" t="n">
-        <v>79657</v>
+        <v>90693</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8515,21 +8510,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8539,10 +8534,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387056</v>
+        <v>386906</v>
       </c>
       <c r="R77" t="n">
-        <v>6723350</v>
+        <v>6723248</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8601,7 +8596,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672252</v>
+        <v>121672247</v>
       </c>
       <c r="B78" t="n">
         <v>90693</v>
@@ -8641,10 +8636,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>386906</v>
+        <v>387273</v>
       </c>
       <c r="R78" t="n">
-        <v>6723248</v>
+        <v>6723412</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8703,10 +8698,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672243</v>
+        <v>121672254</v>
       </c>
       <c r="B79" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8719,21 +8714,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8743,10 +8738,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>388056</v>
+        <v>387774</v>
       </c>
       <c r="R79" t="n">
-        <v>6723670</v>
+        <v>6723594</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8805,10 +8800,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121672248</v>
+        <v>121672251</v>
       </c>
       <c r="B80" t="n">
-        <v>79234</v>
+        <v>79697</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8821,21 +8816,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8845,10 +8840,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>387664</v>
+        <v>387205</v>
       </c>
       <c r="R80" t="n">
-        <v>6723537</v>
+        <v>6723389</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8907,10 +8902,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672247</v>
+        <v>121672250</v>
       </c>
       <c r="B81" t="n">
-        <v>90693</v>
+        <v>78650</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8919,25 +8914,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8947,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>387273</v>
+        <v>386886</v>
       </c>
       <c r="R81" t="n">
-        <v>6723412</v>
+        <v>6723261</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8983,6 +8978,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7464,10 +7464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672255</v>
+        <v>121672244</v>
       </c>
       <c r="B67" t="n">
-        <v>79657</v>
+        <v>78650</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7476,25 +7476,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387034</v>
+        <v>387777</v>
       </c>
       <c r="R67" t="n">
-        <v>6723332</v>
+        <v>6723536</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672244</v>
+        <v>121672255</v>
       </c>
       <c r="B68" t="n">
-        <v>78650</v>
+        <v>79657</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7578,25 +7578,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387777</v>
+        <v>387034</v>
       </c>
       <c r="R68" t="n">
-        <v>6723536</v>
+        <v>6723332</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7362,7 +7362,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672245</v>
+        <v>121672255</v>
       </c>
       <c r="B66" t="n">
         <v>79657</v>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387056</v>
+        <v>387034</v>
       </c>
       <c r="R66" t="n">
-        <v>6723350</v>
+        <v>6723332</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672244</v>
+        <v>121672239</v>
       </c>
       <c r="B67" t="n">
-        <v>78650</v>
+        <v>90728</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7480,21 +7480,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387777</v>
+        <v>387391</v>
       </c>
       <c r="R67" t="n">
-        <v>6723536</v>
+        <v>6723451</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672255</v>
+        <v>121672242</v>
       </c>
       <c r="B68" t="n">
-        <v>79657</v>
+        <v>74714</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7578,25 +7578,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387034</v>
+        <v>387833</v>
       </c>
       <c r="R68" t="n">
-        <v>6723332</v>
+        <v>6723529</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7668,10 +7668,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672239</v>
+        <v>121672244</v>
       </c>
       <c r="B69" t="n">
-        <v>90728</v>
+        <v>78650</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7684,21 +7684,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7708,10 +7708,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>387391</v>
+        <v>387777</v>
       </c>
       <c r="R69" t="n">
-        <v>6723451</v>
+        <v>6723536</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7770,10 +7770,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121672242</v>
+        <v>121672245</v>
       </c>
       <c r="B70" t="n">
-        <v>74714</v>
+        <v>79657</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7782,25 +7782,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>387833</v>
+        <v>387056</v>
       </c>
       <c r="R70" t="n">
-        <v>6723529</v>
+        <v>6723350</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7872,10 +7872,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672248</v>
+        <v>121672252</v>
       </c>
       <c r="B71" t="n">
-        <v>79234</v>
+        <v>90693</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7884,25 +7884,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387664</v>
+        <v>386906</v>
       </c>
       <c r="R71" t="n">
-        <v>6723537</v>
+        <v>6723248</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7974,10 +7974,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672240</v>
+        <v>121672249</v>
       </c>
       <c r="B72" t="n">
-        <v>90746</v>
+        <v>79697</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7990,21 +7990,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387775</v>
+        <v>386886</v>
       </c>
       <c r="R72" t="n">
-        <v>6723585</v>
+        <v>6723261</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8050,6 +8050,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8183,10 +8188,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672249</v>
+        <v>121672240</v>
       </c>
       <c r="B74" t="n">
-        <v>79697</v>
+        <v>90746</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8199,21 +8204,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8223,10 +8228,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>386886</v>
+        <v>387775</v>
       </c>
       <c r="R74" t="n">
-        <v>6723261</v>
+        <v>6723585</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8259,11 +8264,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8290,10 +8290,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672243</v>
+        <v>121672254</v>
       </c>
       <c r="B75" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8306,21 +8306,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>388056</v>
+        <v>387774</v>
       </c>
       <c r="R75" t="n">
-        <v>6723670</v>
+        <v>6723594</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8392,10 +8392,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672246</v>
+        <v>121672243</v>
       </c>
       <c r="B76" t="n">
-        <v>79698</v>
+        <v>90746</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8408,21 +8408,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8432,10 +8432,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387932</v>
+        <v>388056</v>
       </c>
       <c r="R76" t="n">
-        <v>6723626</v>
+        <v>6723670</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8494,10 +8494,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672252</v>
+        <v>121672250</v>
       </c>
       <c r="B77" t="n">
-        <v>90693</v>
+        <v>78650</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8506,25 +8506,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8534,10 +8534,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>386906</v>
+        <v>386886</v>
       </c>
       <c r="R77" t="n">
-        <v>6723248</v>
+        <v>6723261</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,6 +8570,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8596,10 +8601,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672247</v>
+        <v>121672248</v>
       </c>
       <c r="B78" t="n">
-        <v>90693</v>
+        <v>79234</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8608,25 +8613,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8636,10 +8641,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>387273</v>
+        <v>387664</v>
       </c>
       <c r="R78" t="n">
-        <v>6723412</v>
+        <v>6723537</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8698,10 +8703,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672254</v>
+        <v>121672246</v>
       </c>
       <c r="B79" t="n">
-        <v>90728</v>
+        <v>79698</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8714,21 +8719,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8738,10 +8743,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>387774</v>
+        <v>387932</v>
       </c>
       <c r="R79" t="n">
-        <v>6723594</v>
+        <v>6723626</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8800,10 +8805,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121672251</v>
+        <v>121672247</v>
       </c>
       <c r="B80" t="n">
-        <v>79697</v>
+        <v>90693</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8812,25 +8817,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8840,10 +8845,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>387205</v>
+        <v>387273</v>
       </c>
       <c r="R80" t="n">
-        <v>6723389</v>
+        <v>6723412</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8902,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672250</v>
+        <v>121672251</v>
       </c>
       <c r="B81" t="n">
-        <v>78650</v>
+        <v>79697</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8918,21 +8923,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8942,10 +8947,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>386886</v>
+        <v>387205</v>
       </c>
       <c r="R81" t="n">
-        <v>6723261</v>
+        <v>6723389</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8978,11 +8983,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672255</v>
+        <v>121672244</v>
       </c>
       <c r="B66" t="n">
-        <v>79657</v>
+        <v>78650</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7374,25 +7374,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387034</v>
+        <v>387777</v>
       </c>
       <c r="R66" t="n">
-        <v>6723332</v>
+        <v>6723536</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672239</v>
+        <v>121672250</v>
       </c>
       <c r="B67" t="n">
-        <v>90728</v>
+        <v>78650</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7480,21 +7480,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387391</v>
+        <v>386886</v>
       </c>
       <c r="R67" t="n">
-        <v>6723451</v>
+        <v>6723261</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7540,6 +7540,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7566,10 +7571,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672242</v>
+        <v>121672240</v>
       </c>
       <c r="B68" t="n">
-        <v>74714</v>
+        <v>90746</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7582,21 +7587,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7606,10 +7611,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387833</v>
+        <v>387775</v>
       </c>
       <c r="R68" t="n">
-        <v>6723529</v>
+        <v>6723585</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7668,10 +7673,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672244</v>
+        <v>121672247</v>
       </c>
       <c r="B69" t="n">
-        <v>78650</v>
+        <v>90693</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7680,25 +7685,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7708,10 +7713,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>387777</v>
+        <v>387273</v>
       </c>
       <c r="R69" t="n">
-        <v>6723536</v>
+        <v>6723412</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7770,10 +7775,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121672245</v>
+        <v>121672246</v>
       </c>
       <c r="B70" t="n">
-        <v>79657</v>
+        <v>79698</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7782,25 +7787,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7810,10 +7815,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>387056</v>
+        <v>387932</v>
       </c>
       <c r="R70" t="n">
-        <v>6723350</v>
+        <v>6723626</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7872,10 +7877,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672252</v>
+        <v>121672245</v>
       </c>
       <c r="B71" t="n">
-        <v>90693</v>
+        <v>79657</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7888,21 +7893,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7912,10 +7917,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>386906</v>
+        <v>387056</v>
       </c>
       <c r="R71" t="n">
-        <v>6723248</v>
+        <v>6723350</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7974,10 +7979,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672249</v>
+        <v>121672242</v>
       </c>
       <c r="B72" t="n">
-        <v>79697</v>
+        <v>74714</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7990,21 +7995,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8014,10 +8019,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>386886</v>
+        <v>387833</v>
       </c>
       <c r="R72" t="n">
-        <v>6723261</v>
+        <v>6723529</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8050,11 +8055,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8081,7 +8081,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121672241</v>
+        <v>121672251</v>
       </c>
       <c r="B73" t="n">
         <v>79697</v>
@@ -8121,10 +8121,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>386889</v>
+        <v>387205</v>
       </c>
       <c r="R73" t="n">
-        <v>6723271</v>
+        <v>6723389</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8157,11 +8157,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8188,7 +8183,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672240</v>
+        <v>121672243</v>
       </c>
       <c r="B74" t="n">
         <v>90746</v>
@@ -8228,10 +8223,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387775</v>
+        <v>388056</v>
       </c>
       <c r="R74" t="n">
-        <v>6723585</v>
+        <v>6723670</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8290,10 +8285,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672254</v>
+        <v>121672255</v>
       </c>
       <c r="B75" t="n">
-        <v>90728</v>
+        <v>79657</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8302,25 +8297,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8330,10 +8325,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387774</v>
+        <v>387034</v>
       </c>
       <c r="R75" t="n">
-        <v>6723594</v>
+        <v>6723332</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8392,10 +8387,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672243</v>
+        <v>121672239</v>
       </c>
       <c r="B76" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8408,21 +8403,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8432,10 +8427,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>388056</v>
+        <v>387391</v>
       </c>
       <c r="R76" t="n">
-        <v>6723670</v>
+        <v>6723451</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8494,10 +8489,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672250</v>
+        <v>121672252</v>
       </c>
       <c r="B77" t="n">
-        <v>78650</v>
+        <v>90693</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8506,25 +8501,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8534,10 +8529,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>386886</v>
+        <v>386906</v>
       </c>
       <c r="R77" t="n">
-        <v>6723261</v>
+        <v>6723248</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,11 +8565,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8601,10 +8591,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672248</v>
+        <v>121672241</v>
       </c>
       <c r="B78" t="n">
-        <v>79234</v>
+        <v>79697</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8617,21 +8607,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8641,10 +8631,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>387664</v>
+        <v>386889</v>
       </c>
       <c r="R78" t="n">
-        <v>6723537</v>
+        <v>6723271</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8677,6 +8667,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8703,10 +8698,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672246</v>
+        <v>121672254</v>
       </c>
       <c r="B79" t="n">
-        <v>79698</v>
+        <v>90728</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8719,21 +8714,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8743,10 +8738,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>387932</v>
+        <v>387774</v>
       </c>
       <c r="R79" t="n">
-        <v>6723626</v>
+        <v>6723594</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8805,10 +8800,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121672247</v>
+        <v>121672248</v>
       </c>
       <c r="B80" t="n">
-        <v>90693</v>
+        <v>79234</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8817,25 +8812,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8845,10 +8840,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>387273</v>
+        <v>387664</v>
       </c>
       <c r="R80" t="n">
-        <v>6723412</v>
+        <v>6723537</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8907,7 +8902,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672251</v>
+        <v>121672249</v>
       </c>
       <c r="B81" t="n">
         <v>79697</v>
@@ -8947,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>387205</v>
+        <v>386886</v>
       </c>
       <c r="R81" t="n">
-        <v>6723389</v>
+        <v>6723261</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8983,6 +8978,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672244</v>
+        <v>121672239</v>
       </c>
       <c r="B66" t="n">
-        <v>78650</v>
+        <v>90728</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7378,21 +7378,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387777</v>
+        <v>387391</v>
       </c>
       <c r="R66" t="n">
-        <v>6723536</v>
+        <v>6723451</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672250</v>
+        <v>121672252</v>
       </c>
       <c r="B67" t="n">
-        <v>78650</v>
+        <v>90693</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7476,25 +7476,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>386886</v>
+        <v>386906</v>
       </c>
       <c r="R67" t="n">
-        <v>6723261</v>
+        <v>6723248</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7540,11 +7540,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7571,10 +7566,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672240</v>
+        <v>121672241</v>
       </c>
       <c r="B68" t="n">
-        <v>90746</v>
+        <v>79697</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7587,21 +7582,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7611,10 +7606,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387775</v>
+        <v>386889</v>
       </c>
       <c r="R68" t="n">
-        <v>6723585</v>
+        <v>6723271</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7647,6 +7642,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7673,10 +7673,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672247</v>
+        <v>121672244</v>
       </c>
       <c r="B69" t="n">
-        <v>90693</v>
+        <v>78650</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7685,25 +7685,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>387273</v>
+        <v>387777</v>
       </c>
       <c r="R69" t="n">
-        <v>6723412</v>
+        <v>6723536</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121672246</v>
+        <v>121672245</v>
       </c>
       <c r="B70" t="n">
-        <v>79698</v>
+        <v>79657</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7787,25 +7787,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>387932</v>
+        <v>387056</v>
       </c>
       <c r="R70" t="n">
-        <v>6723626</v>
+        <v>6723350</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7877,10 +7877,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672245</v>
+        <v>121672249</v>
       </c>
       <c r="B71" t="n">
-        <v>79657</v>
+        <v>79697</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7889,25 +7889,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7917,10 +7917,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387056</v>
+        <v>386886</v>
       </c>
       <c r="R71" t="n">
-        <v>6723350</v>
+        <v>6723261</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7953,6 +7953,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7979,10 +7984,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672242</v>
+        <v>121672240</v>
       </c>
       <c r="B72" t="n">
-        <v>74714</v>
+        <v>90746</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7995,21 +8000,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8019,10 +8024,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387833</v>
+        <v>387775</v>
       </c>
       <c r="R72" t="n">
-        <v>6723529</v>
+        <v>6723585</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8081,10 +8086,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121672251</v>
+        <v>121672247</v>
       </c>
       <c r="B73" t="n">
-        <v>79697</v>
+        <v>90693</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8093,25 +8098,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8121,10 +8126,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387205</v>
+        <v>387273</v>
       </c>
       <c r="R73" t="n">
-        <v>6723389</v>
+        <v>6723412</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8285,10 +8290,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672255</v>
+        <v>121672251</v>
       </c>
       <c r="B75" t="n">
-        <v>79657</v>
+        <v>79697</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8297,25 +8302,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8325,10 +8330,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387034</v>
+        <v>387205</v>
       </c>
       <c r="R75" t="n">
-        <v>6723332</v>
+        <v>6723389</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8387,7 +8392,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672239</v>
+        <v>121672254</v>
       </c>
       <c r="B76" t="n">
         <v>90728</v>
@@ -8427,10 +8432,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387391</v>
+        <v>387774</v>
       </c>
       <c r="R76" t="n">
-        <v>6723451</v>
+        <v>6723594</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8489,10 +8494,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672252</v>
+        <v>121672255</v>
       </c>
       <c r="B77" t="n">
-        <v>90693</v>
+        <v>79657</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8505,21 +8510,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8529,10 +8534,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>386906</v>
+        <v>387034</v>
       </c>
       <c r="R77" t="n">
-        <v>6723248</v>
+        <v>6723332</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8591,10 +8596,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672241</v>
+        <v>121672246</v>
       </c>
       <c r="B78" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8607,21 +8612,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8631,10 +8636,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>386889</v>
+        <v>387932</v>
       </c>
       <c r="R78" t="n">
-        <v>6723271</v>
+        <v>6723626</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8667,11 +8672,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8698,10 +8698,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672254</v>
+        <v>121672250</v>
       </c>
       <c r="B79" t="n">
-        <v>90728</v>
+        <v>78650</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8714,21 +8714,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>387774</v>
+        <v>386886</v>
       </c>
       <c r="R79" t="n">
-        <v>6723594</v>
+        <v>6723261</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8774,6 +8774,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8902,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672249</v>
+        <v>121672242</v>
       </c>
       <c r="B81" t="n">
-        <v>79697</v>
+        <v>74714</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8918,21 +8923,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8942,10 +8947,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>386886</v>
+        <v>387833</v>
       </c>
       <c r="R81" t="n">
-        <v>6723261</v>
+        <v>6723529</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8978,11 +8983,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672239</v>
+        <v>121672249</v>
       </c>
       <c r="B66" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7378,21 +7378,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387391</v>
+        <v>386886</v>
       </c>
       <c r="R66" t="n">
-        <v>6723451</v>
+        <v>6723261</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7438,6 +7438,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7566,7 +7571,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672241</v>
+        <v>121672251</v>
       </c>
       <c r="B68" t="n">
         <v>79697</v>
@@ -7606,10 +7611,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>386889</v>
+        <v>387205</v>
       </c>
       <c r="R68" t="n">
-        <v>6723271</v>
+        <v>6723389</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,11 +7647,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7673,10 +7673,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672244</v>
+        <v>121672246</v>
       </c>
       <c r="B69" t="n">
-        <v>78650</v>
+        <v>79698</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7689,21 +7689,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7713,10 +7713,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>387777</v>
+        <v>387932</v>
       </c>
       <c r="R69" t="n">
-        <v>6723536</v>
+        <v>6723626</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121672245</v>
+        <v>121672241</v>
       </c>
       <c r="B70" t="n">
-        <v>79657</v>
+        <v>79697</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7787,25 +7787,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>387056</v>
+        <v>386889</v>
       </c>
       <c r="R70" t="n">
-        <v>6723350</v>
+        <v>6723271</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7851,6 +7851,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7877,10 +7882,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672249</v>
+        <v>121672248</v>
       </c>
       <c r="B71" t="n">
-        <v>79697</v>
+        <v>79234</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7893,21 +7898,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7917,10 +7922,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>386886</v>
+        <v>387664</v>
       </c>
       <c r="R71" t="n">
-        <v>6723261</v>
+        <v>6723537</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7953,11 +7958,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7984,10 +7984,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672240</v>
+        <v>121672247</v>
       </c>
       <c r="B72" t="n">
-        <v>90746</v>
+        <v>90693</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7996,25 +7996,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8024,10 +8024,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387775</v>
+        <v>387273</v>
       </c>
       <c r="R72" t="n">
-        <v>6723585</v>
+        <v>6723412</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8086,10 +8086,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121672247</v>
+        <v>121672254</v>
       </c>
       <c r="B73" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8098,25 +8098,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8126,10 +8126,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387273</v>
+        <v>387774</v>
       </c>
       <c r="R73" t="n">
-        <v>6723412</v>
+        <v>6723594</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8188,10 +8188,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672243</v>
+        <v>121672245</v>
       </c>
       <c r="B74" t="n">
-        <v>90746</v>
+        <v>79657</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8200,25 +8200,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>388056</v>
+        <v>387056</v>
       </c>
       <c r="R74" t="n">
-        <v>6723670</v>
+        <v>6723350</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8290,10 +8290,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672251</v>
+        <v>121672250</v>
       </c>
       <c r="B75" t="n">
-        <v>79697</v>
+        <v>78650</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8306,21 +8306,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387205</v>
+        <v>386886</v>
       </c>
       <c r="R75" t="n">
-        <v>6723389</v>
+        <v>6723261</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8366,6 +8366,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8392,10 +8397,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672254</v>
+        <v>121672242</v>
       </c>
       <c r="B76" t="n">
-        <v>90728</v>
+        <v>74714</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8408,21 +8413,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8432,10 +8437,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387774</v>
+        <v>387833</v>
       </c>
       <c r="R76" t="n">
-        <v>6723594</v>
+        <v>6723529</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8494,10 +8499,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672255</v>
+        <v>121672240</v>
       </c>
       <c r="B77" t="n">
-        <v>79657</v>
+        <v>90746</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8506,25 +8511,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8534,10 +8539,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387034</v>
+        <v>387775</v>
       </c>
       <c r="R77" t="n">
-        <v>6723332</v>
+        <v>6723585</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8596,10 +8601,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672246</v>
+        <v>121672243</v>
       </c>
       <c r="B78" t="n">
-        <v>79698</v>
+        <v>90746</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8612,21 +8617,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8636,10 +8641,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>387932</v>
+        <v>388056</v>
       </c>
       <c r="R78" t="n">
-        <v>6723626</v>
+        <v>6723670</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8698,7 +8703,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672250</v>
+        <v>121672244</v>
       </c>
       <c r="B79" t="n">
         <v>78650</v>
@@ -8738,10 +8743,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>386886</v>
+        <v>387777</v>
       </c>
       <c r="R79" t="n">
-        <v>6723261</v>
+        <v>6723536</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8774,11 +8779,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8805,10 +8805,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121672248</v>
+        <v>121672255</v>
       </c>
       <c r="B80" t="n">
-        <v>79234</v>
+        <v>79657</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8817,25 +8817,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8845,10 +8845,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>387664</v>
+        <v>387034</v>
       </c>
       <c r="R80" t="n">
-        <v>6723537</v>
+        <v>6723332</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8907,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672242</v>
+        <v>121672239</v>
       </c>
       <c r="B81" t="n">
-        <v>74714</v>
+        <v>90728</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8923,21 +8923,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>387833</v>
+        <v>387391</v>
       </c>
       <c r="R81" t="n">
-        <v>6723529</v>
+        <v>6723451</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672249</v>
+        <v>121672239</v>
       </c>
       <c r="B66" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7378,21 +7378,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>386886</v>
+        <v>387391</v>
       </c>
       <c r="R66" t="n">
-        <v>6723261</v>
+        <v>6723451</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7438,11 +7438,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7469,10 +7464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672252</v>
+        <v>121672240</v>
       </c>
       <c r="B67" t="n">
-        <v>90693</v>
+        <v>90746</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7481,25 +7476,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7509,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>386906</v>
+        <v>387775</v>
       </c>
       <c r="R67" t="n">
-        <v>6723248</v>
+        <v>6723585</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7571,10 +7566,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672251</v>
+        <v>121672242</v>
       </c>
       <c r="B68" t="n">
-        <v>79697</v>
+        <v>74714</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7587,21 +7582,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7611,10 +7606,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387205</v>
+        <v>387833</v>
       </c>
       <c r="R68" t="n">
-        <v>6723389</v>
+        <v>6723529</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7673,10 +7668,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672246</v>
+        <v>121672243</v>
       </c>
       <c r="B69" t="n">
-        <v>79698</v>
+        <v>90746</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7689,21 +7684,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7713,10 +7708,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>387932</v>
+        <v>388056</v>
       </c>
       <c r="R69" t="n">
-        <v>6723626</v>
+        <v>6723670</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7775,10 +7770,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121672241</v>
+        <v>121672246</v>
       </c>
       <c r="B70" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7791,21 +7786,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7815,10 +7810,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>386889</v>
+        <v>387932</v>
       </c>
       <c r="R70" t="n">
-        <v>6723271</v>
+        <v>6723626</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7851,11 +7846,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7882,10 +7872,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672248</v>
+        <v>121672255</v>
       </c>
       <c r="B71" t="n">
-        <v>79234</v>
+        <v>79657</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7894,25 +7884,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7922,10 +7912,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387664</v>
+        <v>387034</v>
       </c>
       <c r="R71" t="n">
-        <v>6723537</v>
+        <v>6723332</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7984,10 +7974,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672247</v>
+        <v>121672254</v>
       </c>
       <c r="B72" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7996,25 +7986,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8024,10 +8014,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387273</v>
+        <v>387774</v>
       </c>
       <c r="R72" t="n">
-        <v>6723412</v>
+        <v>6723594</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8086,10 +8076,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121672254</v>
+        <v>121672251</v>
       </c>
       <c r="B73" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8102,21 +8092,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8126,10 +8116,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387774</v>
+        <v>387205</v>
       </c>
       <c r="R73" t="n">
-        <v>6723594</v>
+        <v>6723389</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8188,10 +8178,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672245</v>
+        <v>121672247</v>
       </c>
       <c r="B74" t="n">
-        <v>79657</v>
+        <v>90693</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8204,21 +8194,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8228,10 +8218,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387056</v>
+        <v>387273</v>
       </c>
       <c r="R74" t="n">
-        <v>6723350</v>
+        <v>6723412</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8290,7 +8280,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672250</v>
+        <v>121672244</v>
       </c>
       <c r="B75" t="n">
         <v>78650</v>
@@ -8330,10 +8320,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>386886</v>
+        <v>387777</v>
       </c>
       <c r="R75" t="n">
-        <v>6723261</v>
+        <v>6723536</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8366,11 +8356,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8397,10 +8382,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672242</v>
+        <v>121672248</v>
       </c>
       <c r="B76" t="n">
-        <v>74714</v>
+        <v>79234</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8413,21 +8398,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8437,10 +8422,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387833</v>
+        <v>387664</v>
       </c>
       <c r="R76" t="n">
-        <v>6723529</v>
+        <v>6723537</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8499,10 +8484,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672240</v>
+        <v>121672252</v>
       </c>
       <c r="B77" t="n">
-        <v>90746</v>
+        <v>90693</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8511,25 +8496,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8539,10 +8524,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387775</v>
+        <v>386906</v>
       </c>
       <c r="R77" t="n">
-        <v>6723585</v>
+        <v>6723248</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8601,10 +8586,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672243</v>
+        <v>121672241</v>
       </c>
       <c r="B78" t="n">
-        <v>90746</v>
+        <v>79697</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8617,21 +8602,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8641,10 +8626,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>388056</v>
+        <v>386889</v>
       </c>
       <c r="R78" t="n">
-        <v>6723670</v>
+        <v>6723271</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8677,6 +8662,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8703,10 +8693,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672244</v>
+        <v>121672249</v>
       </c>
       <c r="B79" t="n">
-        <v>78650</v>
+        <v>79697</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8719,21 +8709,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8743,10 +8733,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>387777</v>
+        <v>386886</v>
       </c>
       <c r="R79" t="n">
-        <v>6723536</v>
+        <v>6723261</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8779,6 +8769,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8805,7 +8800,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121672255</v>
+        <v>121672245</v>
       </c>
       <c r="B80" t="n">
         <v>79657</v>
@@ -8845,10 +8840,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>387034</v>
+        <v>387056</v>
       </c>
       <c r="R80" t="n">
-        <v>6723332</v>
+        <v>6723350</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8907,10 +8902,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672239</v>
+        <v>121672250</v>
       </c>
       <c r="B81" t="n">
-        <v>90728</v>
+        <v>78650</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8923,21 +8918,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8947,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>387391</v>
+        <v>386886</v>
       </c>
       <c r="R81" t="n">
-        <v>6723451</v>
+        <v>6723261</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8983,6 +8978,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7464,10 +7464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672240</v>
+        <v>121672242</v>
       </c>
       <c r="B67" t="n">
-        <v>90746</v>
+        <v>74714</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7480,21 +7480,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387775</v>
+        <v>387833</v>
       </c>
       <c r="R67" t="n">
-        <v>6723585</v>
+        <v>6723529</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672242</v>
+        <v>121672240</v>
       </c>
       <c r="B68" t="n">
-        <v>74714</v>
+        <v>90746</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7582,21 +7582,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387833</v>
+        <v>387775</v>
       </c>
       <c r="R68" t="n">
-        <v>6723529</v>
+        <v>6723585</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7974,10 +7974,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672254</v>
+        <v>121672251</v>
       </c>
       <c r="B72" t="n">
-        <v>90728</v>
+        <v>79697</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7990,21 +7990,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387774</v>
+        <v>387205</v>
       </c>
       <c r="R72" t="n">
-        <v>6723594</v>
+        <v>6723389</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8076,10 +8076,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121672251</v>
+        <v>121672254</v>
       </c>
       <c r="B73" t="n">
-        <v>79697</v>
+        <v>90728</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8092,21 +8092,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8116,10 +8116,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387205</v>
+        <v>387774</v>
       </c>
       <c r="R73" t="n">
-        <v>6723389</v>
+        <v>6723594</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8484,10 +8484,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672252</v>
+        <v>121672241</v>
       </c>
       <c r="B77" t="n">
-        <v>90693</v>
+        <v>79697</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8496,25 +8496,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8524,10 +8524,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>386906</v>
+        <v>386889</v>
       </c>
       <c r="R77" t="n">
-        <v>6723248</v>
+        <v>6723271</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8560,6 +8560,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8586,10 +8591,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672241</v>
+        <v>121672252</v>
       </c>
       <c r="B78" t="n">
-        <v>79697</v>
+        <v>90693</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8598,25 +8603,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8626,10 +8631,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>386889</v>
+        <v>386906</v>
       </c>
       <c r="R78" t="n">
-        <v>6723271</v>
+        <v>6723248</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8662,11 +8667,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672239</v>
+        <v>121672254</v>
       </c>
       <c r="B66" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387391</v>
+        <v>387774</v>
       </c>
       <c r="R66" t="n">
-        <v>6723451</v>
+        <v>6723594</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672242</v>
+        <v>121672249</v>
       </c>
       <c r="B67" t="n">
-        <v>74714</v>
+        <v>79710</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7480,21 +7480,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387833</v>
+        <v>386886</v>
       </c>
       <c r="R67" t="n">
-        <v>6723529</v>
+        <v>6723261</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7540,6 +7540,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7566,10 +7571,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672240</v>
+        <v>121672241</v>
       </c>
       <c r="B68" t="n">
-        <v>90746</v>
+        <v>79710</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7582,21 +7587,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7606,10 +7611,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387775</v>
+        <v>386889</v>
       </c>
       <c r="R68" t="n">
-        <v>6723585</v>
+        <v>6723271</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,6 +7647,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7668,10 +7678,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672243</v>
+        <v>121672245</v>
       </c>
       <c r="B69" t="n">
-        <v>90746</v>
+        <v>79670</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7680,25 +7690,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7708,10 +7718,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>388056</v>
+        <v>387056</v>
       </c>
       <c r="R69" t="n">
-        <v>6723670</v>
+        <v>6723350</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7770,10 +7780,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121672246</v>
+        <v>121672251</v>
       </c>
       <c r="B70" t="n">
-        <v>79698</v>
+        <v>79710</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7786,21 +7796,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7810,10 +7820,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>387932</v>
+        <v>387205</v>
       </c>
       <c r="R70" t="n">
-        <v>6723626</v>
+        <v>6723389</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7872,10 +7882,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672255</v>
+        <v>121672240</v>
       </c>
       <c r="B71" t="n">
-        <v>79657</v>
+        <v>90760</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7884,25 +7894,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7912,10 +7922,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387034</v>
+        <v>387775</v>
       </c>
       <c r="R71" t="n">
-        <v>6723332</v>
+        <v>6723585</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7974,10 +7984,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672251</v>
+        <v>121672250</v>
       </c>
       <c r="B72" t="n">
-        <v>79697</v>
+        <v>78663</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7990,21 +8000,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8014,10 +8024,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387205</v>
+        <v>386886</v>
       </c>
       <c r="R72" t="n">
-        <v>6723389</v>
+        <v>6723261</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8050,6 +8060,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8076,10 +8091,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121672254</v>
+        <v>121672248</v>
       </c>
       <c r="B73" t="n">
-        <v>90728</v>
+        <v>79247</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8092,21 +8107,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8116,10 +8131,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387774</v>
+        <v>387664</v>
       </c>
       <c r="R73" t="n">
-        <v>6723594</v>
+        <v>6723537</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8178,10 +8193,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672247</v>
+        <v>121672246</v>
       </c>
       <c r="B74" t="n">
-        <v>90693</v>
+        <v>79711</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8190,25 +8205,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8218,10 +8233,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387273</v>
+        <v>387932</v>
       </c>
       <c r="R74" t="n">
-        <v>6723412</v>
+        <v>6723626</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8280,10 +8295,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672244</v>
+        <v>121672252</v>
       </c>
       <c r="B75" t="n">
-        <v>78650</v>
+        <v>90707</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8292,25 +8307,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8320,10 +8335,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387777</v>
+        <v>386906</v>
       </c>
       <c r="R75" t="n">
-        <v>6723536</v>
+        <v>6723248</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8382,10 +8397,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672248</v>
+        <v>121672255</v>
       </c>
       <c r="B76" t="n">
-        <v>79234</v>
+        <v>79670</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8394,25 +8409,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8422,10 +8437,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387664</v>
+        <v>387034</v>
       </c>
       <c r="R76" t="n">
-        <v>6723537</v>
+        <v>6723332</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8484,10 +8499,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672241</v>
+        <v>121672244</v>
       </c>
       <c r="B77" t="n">
-        <v>79697</v>
+        <v>78663</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8500,21 +8515,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8524,10 +8539,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>386889</v>
+        <v>387777</v>
       </c>
       <c r="R77" t="n">
-        <v>6723271</v>
+        <v>6723536</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8560,11 +8575,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8591,10 +8601,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672252</v>
+        <v>121672239</v>
       </c>
       <c r="B78" t="n">
-        <v>90693</v>
+        <v>90742</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8603,25 +8613,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8631,10 +8641,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>386906</v>
+        <v>387391</v>
       </c>
       <c r="R78" t="n">
-        <v>6723248</v>
+        <v>6723451</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8693,10 +8703,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672249</v>
+        <v>121672247</v>
       </c>
       <c r="B79" t="n">
-        <v>79697</v>
+        <v>90707</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8705,25 +8715,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8733,10 +8743,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>386886</v>
+        <v>387273</v>
       </c>
       <c r="R79" t="n">
-        <v>6723261</v>
+        <v>6723412</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8769,11 +8779,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8800,10 +8805,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121672245</v>
+        <v>121672242</v>
       </c>
       <c r="B80" t="n">
-        <v>79657</v>
+        <v>74727</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8812,25 +8817,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8840,10 +8845,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>387056</v>
+        <v>387833</v>
       </c>
       <c r="R80" t="n">
-        <v>6723350</v>
+        <v>6723529</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8902,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672250</v>
+        <v>121672243</v>
       </c>
       <c r="B81" t="n">
-        <v>78650</v>
+        <v>90760</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8918,21 +8923,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8942,10 +8947,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>386886</v>
+        <v>388056</v>
       </c>
       <c r="R81" t="n">
-        <v>6723261</v>
+        <v>6723670</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8978,11 +8983,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -8397,10 +8397,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672255</v>
+        <v>121672244</v>
       </c>
       <c r="B76" t="n">
-        <v>79670</v>
+        <v>78663</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8409,25 +8409,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387034</v>
+        <v>387777</v>
       </c>
       <c r="R76" t="n">
-        <v>6723332</v>
+        <v>6723536</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8499,10 +8499,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672244</v>
+        <v>121672239</v>
       </c>
       <c r="B77" t="n">
-        <v>78663</v>
+        <v>90742</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8515,21 +8515,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387777</v>
+        <v>387391</v>
       </c>
       <c r="R77" t="n">
-        <v>6723536</v>
+        <v>6723451</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8601,10 +8601,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672239</v>
+        <v>121672255</v>
       </c>
       <c r="B78" t="n">
-        <v>90742</v>
+        <v>79670</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8613,25 +8613,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8641,10 +8641,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>387391</v>
+        <v>387034</v>
       </c>
       <c r="R78" t="n">
-        <v>6723451</v>
+        <v>6723332</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672254</v>
+        <v>121672240</v>
       </c>
       <c r="B66" t="n">
-        <v>90742</v>
+        <v>90762</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7378,21 +7378,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387774</v>
+        <v>387775</v>
       </c>
       <c r="R66" t="n">
-        <v>6723594</v>
+        <v>6723585</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672249</v>
+        <v>121672255</v>
       </c>
       <c r="B67" t="n">
-        <v>79710</v>
+        <v>79672</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7476,25 +7476,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>386886</v>
+        <v>387034</v>
       </c>
       <c r="R67" t="n">
-        <v>6723261</v>
+        <v>6723332</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7540,11 +7540,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7574,7 +7569,7 @@
         <v>121672241</v>
       </c>
       <c r="B68" t="n">
-        <v>79710</v>
+        <v>79712</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7678,10 +7673,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672245</v>
+        <v>121672248</v>
       </c>
       <c r="B69" t="n">
-        <v>79670</v>
+        <v>79249</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7690,25 +7685,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7718,10 +7713,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>387056</v>
+        <v>387664</v>
       </c>
       <c r="R69" t="n">
-        <v>6723350</v>
+        <v>6723537</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7780,10 +7775,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121672251</v>
+        <v>121672250</v>
       </c>
       <c r="B70" t="n">
-        <v>79710</v>
+        <v>78665</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7796,21 +7791,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7820,10 +7815,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>387205</v>
+        <v>386886</v>
       </c>
       <c r="R70" t="n">
-        <v>6723389</v>
+        <v>6723261</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7856,6 +7851,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7882,10 +7882,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672240</v>
+        <v>121672239</v>
       </c>
       <c r="B71" t="n">
-        <v>90760</v>
+        <v>90744</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7898,21 +7898,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387775</v>
+        <v>387391</v>
       </c>
       <c r="R71" t="n">
-        <v>6723585</v>
+        <v>6723451</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7984,10 +7984,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672250</v>
+        <v>121672244</v>
       </c>
       <c r="B72" t="n">
-        <v>78663</v>
+        <v>78665</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8024,10 +8024,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>386886</v>
+        <v>387777</v>
       </c>
       <c r="R72" t="n">
-        <v>6723261</v>
+        <v>6723536</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8060,11 +8060,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8091,10 +8086,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121672248</v>
+        <v>121672249</v>
       </c>
       <c r="B73" t="n">
-        <v>79247</v>
+        <v>79712</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8107,21 +8102,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8131,10 +8126,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387664</v>
+        <v>386886</v>
       </c>
       <c r="R73" t="n">
-        <v>6723537</v>
+        <v>6723261</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8167,6 +8162,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8193,10 +8193,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672246</v>
+        <v>121672252</v>
       </c>
       <c r="B74" t="n">
-        <v>79711</v>
+        <v>90709</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8205,25 +8205,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8233,10 +8233,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387932</v>
+        <v>386906</v>
       </c>
       <c r="R74" t="n">
-        <v>6723626</v>
+        <v>6723248</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8295,10 +8295,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672252</v>
+        <v>121672243</v>
       </c>
       <c r="B75" t="n">
-        <v>90707</v>
+        <v>90762</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8307,25 +8307,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8335,10 +8335,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>386906</v>
+        <v>388056</v>
       </c>
       <c r="R75" t="n">
-        <v>6723248</v>
+        <v>6723670</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8397,10 +8397,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672244</v>
+        <v>121672246</v>
       </c>
       <c r="B76" t="n">
-        <v>78663</v>
+        <v>79713</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8413,21 +8413,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387777</v>
+        <v>387932</v>
       </c>
       <c r="R76" t="n">
-        <v>6723536</v>
+        <v>6723626</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8499,10 +8499,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672239</v>
+        <v>121672251</v>
       </c>
       <c r="B77" t="n">
-        <v>90742</v>
+        <v>79712</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8515,21 +8515,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387391</v>
+        <v>387205</v>
       </c>
       <c r="R77" t="n">
-        <v>6723451</v>
+        <v>6723389</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8601,10 +8601,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672255</v>
+        <v>121672245</v>
       </c>
       <c r="B78" t="n">
-        <v>79670</v>
+        <v>79672</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8641,10 +8641,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>387034</v>
+        <v>387056</v>
       </c>
       <c r="R78" t="n">
-        <v>6723332</v>
+        <v>6723350</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8703,10 +8703,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672247</v>
+        <v>121672254</v>
       </c>
       <c r="B79" t="n">
-        <v>90707</v>
+        <v>90744</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8715,25 +8715,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>387273</v>
+        <v>387774</v>
       </c>
       <c r="R79" t="n">
-        <v>6723412</v>
+        <v>6723594</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8808,7 +8808,7 @@
         <v>121672242</v>
       </c>
       <c r="B80" t="n">
-        <v>74727</v>
+        <v>74729</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8907,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672243</v>
+        <v>121672247</v>
       </c>
       <c r="B81" t="n">
-        <v>90760</v>
+        <v>90709</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8919,25 +8919,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>388056</v>
+        <v>387273</v>
       </c>
       <c r="R81" t="n">
-        <v>6723670</v>
+        <v>6723412</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672240</v>
+        <v>121672251</v>
       </c>
       <c r="B66" t="n">
-        <v>90762</v>
+        <v>79713</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7378,21 +7378,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387775</v>
+        <v>387205</v>
       </c>
       <c r="R66" t="n">
-        <v>6723585</v>
+        <v>6723389</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672255</v>
+        <v>121672254</v>
       </c>
       <c r="B67" t="n">
-        <v>79672</v>
+        <v>90745</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7476,25 +7476,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387034</v>
+        <v>387774</v>
       </c>
       <c r="R67" t="n">
-        <v>6723332</v>
+        <v>6723594</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7566,10 +7566,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672241</v>
+        <v>121672240</v>
       </c>
       <c r="B68" t="n">
-        <v>79712</v>
+        <v>90763</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7582,21 +7582,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7606,10 +7606,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>386889</v>
+        <v>387775</v>
       </c>
       <c r="R68" t="n">
-        <v>6723271</v>
+        <v>6723585</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,11 +7642,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7673,10 +7668,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672248</v>
+        <v>121672243</v>
       </c>
       <c r="B69" t="n">
-        <v>79249</v>
+        <v>90763</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7689,21 +7684,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7713,10 +7708,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>387664</v>
+        <v>388056</v>
       </c>
       <c r="R69" t="n">
-        <v>6723537</v>
+        <v>6723670</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7778,7 +7773,7 @@
         <v>121672250</v>
       </c>
       <c r="B70" t="n">
-        <v>78665</v>
+        <v>78666</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7882,10 +7877,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672239</v>
+        <v>121672249</v>
       </c>
       <c r="B71" t="n">
-        <v>90744</v>
+        <v>79713</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7898,21 +7893,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7922,10 +7917,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>387391</v>
+        <v>386886</v>
       </c>
       <c r="R71" t="n">
-        <v>6723451</v>
+        <v>6723261</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7958,6 +7953,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7984,10 +7984,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672244</v>
+        <v>121672239</v>
       </c>
       <c r="B72" t="n">
-        <v>78665</v>
+        <v>90745</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8000,21 +8000,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8024,10 +8024,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387777</v>
+        <v>387391</v>
       </c>
       <c r="R72" t="n">
-        <v>6723536</v>
+        <v>6723451</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8086,10 +8086,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121672249</v>
+        <v>121672246</v>
       </c>
       <c r="B73" t="n">
-        <v>79712</v>
+        <v>79714</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8102,21 +8102,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8126,10 +8126,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>386886</v>
+        <v>387932</v>
       </c>
       <c r="R73" t="n">
-        <v>6723261</v>
+        <v>6723626</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8162,11 +8162,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På björk.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8193,10 +8188,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672252</v>
+        <v>121672245</v>
       </c>
       <c r="B74" t="n">
-        <v>90709</v>
+        <v>79673</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8209,21 +8204,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8233,10 +8228,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>386906</v>
+        <v>387056</v>
       </c>
       <c r="R74" t="n">
-        <v>6723248</v>
+        <v>6723350</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8295,10 +8290,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672243</v>
+        <v>121672242</v>
       </c>
       <c r="B75" t="n">
-        <v>90762</v>
+        <v>74729</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8311,21 +8306,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8335,10 +8330,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>388056</v>
+        <v>387833</v>
       </c>
       <c r="R75" t="n">
-        <v>6723670</v>
+        <v>6723529</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8397,10 +8392,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672246</v>
+        <v>121672247</v>
       </c>
       <c r="B76" t="n">
-        <v>79713</v>
+        <v>90710</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8409,25 +8404,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8437,10 +8432,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387932</v>
+        <v>387273</v>
       </c>
       <c r="R76" t="n">
-        <v>6723626</v>
+        <v>6723412</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8499,10 +8494,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121672251</v>
+        <v>121672241</v>
       </c>
       <c r="B77" t="n">
-        <v>79712</v>
+        <v>79713</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8539,10 +8534,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>387205</v>
+        <v>386889</v>
       </c>
       <c r="R77" t="n">
-        <v>6723389</v>
+        <v>6723271</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8575,6 +8570,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På död björk.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8601,10 +8601,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672245</v>
+        <v>121672252</v>
       </c>
       <c r="B78" t="n">
-        <v>79672</v>
+        <v>90710</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8617,21 +8617,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8641,10 +8641,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>387056</v>
+        <v>386906</v>
       </c>
       <c r="R78" t="n">
-        <v>6723350</v>
+        <v>6723248</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8703,10 +8703,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672254</v>
+        <v>121672248</v>
       </c>
       <c r="B79" t="n">
-        <v>90744</v>
+        <v>79250</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8719,21 +8719,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>387774</v>
+        <v>387664</v>
       </c>
       <c r="R79" t="n">
-        <v>6723594</v>
+        <v>6723537</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8805,10 +8805,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121672242</v>
+        <v>121672244</v>
       </c>
       <c r="B80" t="n">
-        <v>74729</v>
+        <v>78666</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8821,21 +8821,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>308</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8845,10 +8845,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>387833</v>
+        <v>387777</v>
       </c>
       <c r="R80" t="n">
-        <v>6723529</v>
+        <v>6723536</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8907,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672247</v>
+        <v>121672255</v>
       </c>
       <c r="B81" t="n">
-        <v>90709</v>
+        <v>79673</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8923,21 +8923,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>387273</v>
+        <v>387034</v>
       </c>
       <c r="R81" t="n">
-        <v>6723412</v>
+        <v>6723332</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -8188,10 +8188,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672245</v>
+        <v>121672242</v>
       </c>
       <c r="B74" t="n">
-        <v>79673</v>
+        <v>74729</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8200,25 +8200,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387056</v>
+        <v>387833</v>
       </c>
       <c r="R74" t="n">
-        <v>6723350</v>
+        <v>6723529</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8290,10 +8290,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672242</v>
+        <v>121672245</v>
       </c>
       <c r="B75" t="n">
-        <v>74729</v>
+        <v>79673</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8302,25 +8302,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>229497</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387833</v>
+        <v>387056</v>
       </c>
       <c r="R75" t="n">
-        <v>6723529</v>
+        <v>6723350</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85440031</v>
+        <v>120970931</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SO om Villmyren, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387817.8330446843</v>
+        <v>387533</v>
       </c>
       <c r="R2" t="n">
-        <v>6723589.017400234</v>
+        <v>6723413</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>anders tedeholm, Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85440029</v>
+        <v>120976760</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,39 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SO om Villmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387796.8059009789</v>
+        <v>388074</v>
       </c>
       <c r="R3" t="n">
-        <v>6723514.061020057</v>
+        <v>6723700</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>anders tedeholm, Helena Malmestrand</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85440040</v>
+        <v>96860854</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SO om Villmyren, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>387022.994589519</v>
+        <v>387707</v>
       </c>
       <c r="R4" t="n">
-        <v>6723335.015614972</v>
+        <v>6723574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>anders tedeholm, Helena Malmestrand</t>
+          <t>anders tedeholm, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>85440039</v>
+        <v>96860873</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SO om Villmyren, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>387210.8741705487</v>
+        <v>387717</v>
       </c>
       <c r="R5" t="n">
-        <v>6723382.147174362</v>
+        <v>6723579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>anders tedeholm, Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>85440030</v>
+        <v>96860880</v>
       </c>
       <c r="B6" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SO om Villmyren, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>387748.9494038753</v>
+        <v>387848</v>
       </c>
       <c r="R6" t="n">
-        <v>6723509.172011191</v>
+        <v>6723623</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1153,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>anders tedeholm, Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>94037181</v>
+        <v>120970921</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sydväst om Branäsberget, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388036.4001741578</v>
+        <v>387966</v>
       </c>
       <c r="R7" t="n">
-        <v>6723690.709469706</v>
+        <v>6723628</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Christina Svensson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Christina Svensson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94037179</v>
+        <v>120970922</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,40 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sydväst om Branäsberget, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>387822.181270452</v>
+        <v>387956</v>
       </c>
       <c r="R8" t="n">
-        <v>6723555.003543365</v>
+        <v>6723630</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,27 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Garnlav med apothecier</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,72 +1336,66 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Christina Svensson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christina Svensson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>94037169</v>
+        <v>120970923</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sydväst om Branäsberget, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>387811.2668193838</v>
+        <v>387857</v>
       </c>
       <c r="R9" t="n">
-        <v>6723536.195460811</v>
+        <v>6723518</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,27 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Christina Svensson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christina Svensson, Andreas Larsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96860867</v>
+        <v>120970925</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ö om Andersberget, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>387708.9803273414</v>
+        <v>387824</v>
       </c>
       <c r="R10" t="n">
-        <v>6723567.866467607</v>
+        <v>6723508</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,22 +1541,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>anders tedeholm, Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96860877</v>
+        <v>120970926</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ö om Andersberget, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>387774.7221813232</v>
+        <v>387809</v>
       </c>
       <c r="R11" t="n">
-        <v>6723578.579278398</v>
+        <v>6723508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,22 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,57 +1638,52 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>anders tedeholm, Jan Rees, Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96860858</v>
+        <v>120970927</v>
       </c>
       <c r="B12" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6450</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ö om Andersberget, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>387714.0925585885</v>
+        <v>387791</v>
       </c>
       <c r="R12" t="n">
-        <v>6723574.089646767</v>
+        <v>6723505</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,22 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,57 +1735,52 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>anders tedeholm, Per Gustafsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96860876</v>
+        <v>120976741</v>
       </c>
       <c r="B13" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6450</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ö om Andersberget, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>387711.9281641991</v>
+        <v>387768</v>
       </c>
       <c r="R13" t="n">
-        <v>6723567.774391213</v>
+        <v>6723513</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1996,22 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,27 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96860852</v>
+        <v>120976743</v>
       </c>
       <c r="B14" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,34 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ö om Andersberget, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>387788.6916947784</v>
+        <v>387788</v>
       </c>
       <c r="R14" t="n">
-        <v>6723600.728565263</v>
+        <v>6723519</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2108,22 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,27 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>anders tedeholm, Per Gustafsson</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96860880</v>
+        <v>120976745</v>
       </c>
       <c r="B15" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2186,14 +1967,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ö om Andersberget, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>387848.3824107078</v>
+        <v>387797</v>
       </c>
       <c r="R15" t="n">
-        <v>6723622.433041991</v>
+        <v>6723537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2220,22 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-10-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,27 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120976760</v>
+        <v>120976746</v>
       </c>
       <c r="B16" t="n">
-        <v>95641</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2302,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388074</v>
+        <v>387815</v>
       </c>
       <c r="R16" t="n">
-        <v>6723700</v>
+        <v>6723536</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,50 +2130,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120970943</v>
+        <v>120976752</v>
       </c>
       <c r="B17" t="n">
-        <v>79714</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387078</v>
+        <v>387969</v>
       </c>
       <c r="R17" t="n">
-        <v>6723335</v>
+        <v>6723628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,27 +2215,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120970920</v>
+        <v>120976755</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2482,34 +2238,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388053</v>
+        <v>387971</v>
       </c>
       <c r="R18" t="n">
-        <v>6723664</v>
+        <v>6723631</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,27 +2312,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120970948</v>
+        <v>120976756</v>
       </c>
       <c r="B19" t="n">
-        <v>88031</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,34 +2335,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387470</v>
+        <v>387997</v>
       </c>
       <c r="R19" t="n">
-        <v>6723459</v>
+        <v>6723622</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2658,27 +2409,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120970930</v>
+        <v>120976758</v>
       </c>
       <c r="B20" t="n">
-        <v>82388</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,34 +2432,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387646</v>
+        <v>388026</v>
       </c>
       <c r="R20" t="n">
-        <v>6723530</v>
+        <v>6723646</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2760,27 +2506,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120970939</v>
+        <v>121672244</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,34 +2529,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>S Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>386858</v>
+        <v>387777</v>
       </c>
       <c r="R21" t="n">
-        <v>6723265</v>
+        <v>6723536</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2862,62 +2603,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120970933</v>
+        <v>121672250</v>
       </c>
       <c r="B22" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>S Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>387048</v>
+        <v>386886</v>
       </c>
       <c r="R22" t="n">
-        <v>6723350</v>
+        <v>6723261</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,6 +2688,11 @@
           <t>2024-11-04</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På björk.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2964,27 +2705,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120970928</v>
+        <v>121672242</v>
       </c>
       <c r="B23" t="n">
-        <v>82388</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,34 +2728,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>S Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>387650</v>
+        <v>387833</v>
       </c>
       <c r="R23" t="n">
-        <v>6723547</v>
+        <v>6723529</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3066,27 +2802,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120976756</v>
+        <v>96860852</v>
       </c>
       <c r="B24" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3094,34 +2825,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>387997</v>
+        <v>387788</v>
       </c>
       <c r="R24" t="n">
-        <v>6723622</v>
+        <v>6723601</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3148,12 +2879,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,27 +2899,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120976727</v>
+        <v>96860883</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3196,34 +2922,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>386876</v>
+        <v>387782</v>
       </c>
       <c r="R25" t="n">
-        <v>6723260</v>
+        <v>6723613</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3250,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3270,27 +2996,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120976752</v>
+        <v>120970946</v>
       </c>
       <c r="B26" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3298,34 +3019,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>387969</v>
+        <v>387338</v>
       </c>
       <c r="R26" t="n">
-        <v>6723628</v>
+        <v>6723431</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,27 +3093,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120970924</v>
+        <v>120970948</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3400,21 +3116,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3424,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>387816</v>
+        <v>387470</v>
       </c>
       <c r="R27" t="n">
-        <v>6723527</v>
+        <v>6723459</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3486,15 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120976740</v>
+        <v>120976728</v>
       </c>
       <c r="B28" t="n">
-        <v>80561</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,21 +3213,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3526,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>387671</v>
+        <v>386791</v>
       </c>
       <c r="R28" t="n">
-        <v>6723531</v>
+        <v>6723204</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,37 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120976747</v>
+        <v>120976731</v>
       </c>
       <c r="B29" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3628,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>387814</v>
+        <v>386893</v>
       </c>
       <c r="R29" t="n">
-        <v>6723543</v>
+        <v>6723204</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3690,15 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120976759</v>
+        <v>120976736</v>
       </c>
       <c r="B30" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3706,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3730,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>388030</v>
+        <v>387487</v>
       </c>
       <c r="R30" t="n">
-        <v>6723650</v>
+        <v>6723421</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3792,15 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120976738</v>
+        <v>120976754</v>
       </c>
       <c r="B31" t="n">
-        <v>82388</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3808,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3832,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>387659</v>
+        <v>387963</v>
       </c>
       <c r="R31" t="n">
-        <v>6723515</v>
+        <v>6723633</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3894,15 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120976730</v>
+        <v>120976740</v>
       </c>
       <c r="B32" t="n">
-        <v>82388</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3910,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>1049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3934,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>386895</v>
+        <v>387671</v>
       </c>
       <c r="R32" t="n">
-        <v>6723208</v>
+        <v>6723531</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3996,15 +3687,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120976751</v>
+        <v>96860887</v>
       </c>
       <c r="B33" t="n">
-        <v>79222</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4012,34 +3698,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>387955</v>
+        <v>387800</v>
       </c>
       <c r="R33" t="n">
-        <v>6723604</v>
+        <v>6723610</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4066,12 +3752,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4086,27 +3772,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm, Jan Rees, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120970923</v>
+        <v>121672239</v>
       </c>
       <c r="B34" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4114,34 +3795,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>S Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>387857</v>
+        <v>387391</v>
       </c>
       <c r="R34" t="n">
-        <v>6723518</v>
+        <v>6723451</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4188,27 +3869,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120976744</v>
+        <v>121672253</v>
       </c>
       <c r="B35" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4216,34 +3892,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>S Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>387795</v>
+        <v>387804</v>
       </c>
       <c r="R35" t="n">
-        <v>6723523</v>
+        <v>6723614</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4290,27 +3966,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120976757</v>
+        <v>121672254</v>
       </c>
       <c r="B36" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4318,34 +3989,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>S Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>388006</v>
+        <v>387774</v>
       </c>
       <c r="R36" t="n">
-        <v>6723626</v>
+        <v>6723594</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4392,62 +4063,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120970922</v>
+        <v>96860878</v>
       </c>
       <c r="B37" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>1249</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>387956</v>
+        <v>387795</v>
       </c>
       <c r="R37" t="n">
-        <v>6723630</v>
+        <v>6723614</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4474,12 +4140,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4499,22 +4165,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>anders tedeholm, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120976743</v>
+        <v>85440030</v>
       </c>
       <c r="B38" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,34 +4183,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>SO om Villmyren, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>387788</v>
+        <v>387749</v>
       </c>
       <c r="R38" t="n">
-        <v>6723519</v>
+        <v>6723509</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4576,12 +4237,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4596,27 +4257,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm, Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120970937</v>
+        <v>120970928</v>
       </c>
       <c r="B39" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4624,21 +4280,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4648,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>386898</v>
+        <v>387650</v>
       </c>
       <c r="R39" t="n">
-        <v>6723285</v>
+        <v>6723547</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4710,37 +4366,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120970934</v>
+        <v>120970930</v>
       </c>
       <c r="B40" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>387036</v>
+        <v>387646</v>
       </c>
       <c r="R40" t="n">
-        <v>6723319</v>
+        <v>6723530</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4812,15 +4463,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120976746</v>
+        <v>120976726</v>
       </c>
       <c r="B41" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4828,21 +4474,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4852,10 +4498,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>387815</v>
+        <v>387454</v>
       </c>
       <c r="R41" t="n">
-        <v>6723536</v>
+        <v>6723442</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4914,15 +4560,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120970921</v>
+        <v>120976730</v>
       </c>
       <c r="B42" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4930,34 +4571,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>387966</v>
+        <v>386895</v>
       </c>
       <c r="R42" t="n">
-        <v>6723628</v>
+        <v>6723208</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5004,27 +4645,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120976726</v>
+        <v>120976737</v>
       </c>
       <c r="B43" t="n">
-        <v>82388</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5056,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>387454</v>
+        <v>387485</v>
       </c>
       <c r="R43" t="n">
-        <v>6723442</v>
+        <v>6723418</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5118,15 +4754,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120976745</v>
+        <v>120976738</v>
       </c>
       <c r="B44" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5134,21 +4765,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5158,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>387797</v>
+        <v>387659</v>
       </c>
       <c r="R44" t="n">
-        <v>6723537</v>
+        <v>6723515</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5220,15 +4851,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120970931</v>
+        <v>120976749</v>
       </c>
       <c r="B45" t="n">
-        <v>95641</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5236,34 +4862,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>387533</v>
+        <v>387877</v>
       </c>
       <c r="R45" t="n">
-        <v>6723413</v>
+        <v>6723565</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5310,27 +4936,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120970936</v>
+        <v>121672246</v>
       </c>
       <c r="B46" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5338,34 +4959,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>S Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>386940</v>
+        <v>387932</v>
       </c>
       <c r="R46" t="n">
-        <v>6723292</v>
+        <v>6723626</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5412,65 +5033,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120976734</v>
+        <v>94037169</v>
       </c>
       <c r="B47" t="n">
-        <v>78341</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Sydväst om Branäsberget, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>387161</v>
+        <v>387811</v>
       </c>
       <c r="R47" t="n">
-        <v>6723401</v>
+        <v>6723536</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5494,12 +5110,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5514,27 +5130,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Christina Svensson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Christina Svensson, Andreas Larsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120970942</v>
+        <v>120970934</v>
       </c>
       <c r="B48" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5542,21 +5153,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5566,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>387010</v>
+        <v>387036</v>
       </c>
       <c r="R48" t="n">
-        <v>6723330</v>
+        <v>6723319</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5628,50 +5239,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120976754</v>
+        <v>120970945</v>
       </c>
       <c r="B49" t="n">
-        <v>88031</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>387963</v>
+        <v>387254</v>
       </c>
       <c r="R49" t="n">
-        <v>6723633</v>
+        <v>6723421</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5718,27 +5324,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120976742</v>
+        <v>120976735</v>
       </c>
       <c r="B50" t="n">
-        <v>74694</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5746,21 +5347,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6439</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5770,10 +5371,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>387783</v>
+        <v>387303</v>
       </c>
       <c r="R50" t="n">
-        <v>6723518</v>
+        <v>6723425</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5832,37 +5433,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120976731</v>
+        <v>120976747</v>
       </c>
       <c r="B51" t="n">
-        <v>88031</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5872,10 +5468,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>386893</v>
+        <v>387814</v>
       </c>
       <c r="R51" t="n">
-        <v>6723204</v>
+        <v>6723543</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5934,50 +5530,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120976741</v>
+        <v>121672247</v>
       </c>
       <c r="B52" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>S Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>387768</v>
+        <v>387273</v>
       </c>
       <c r="R52" t="n">
-        <v>6723513</v>
+        <v>6723412</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6024,62 +5615,57 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120976736</v>
+        <v>121672252</v>
       </c>
       <c r="B53" t="n">
-        <v>88031</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>S Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>387487</v>
+        <v>386906</v>
       </c>
       <c r="R53" t="n">
-        <v>6723421</v>
+        <v>6723248</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6126,62 +5712,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120970927</v>
+        <v>85440040</v>
       </c>
       <c r="B54" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>SO om Villmyren, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>387791</v>
+        <v>387023</v>
       </c>
       <c r="R54" t="n">
-        <v>6723505</v>
+        <v>6723335</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6208,12 +5789,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6233,26 +5814,21 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>anders tedeholm, Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120976748</v>
+        <v>94037179</v>
       </c>
       <c r="B55" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6274,19 +5850,22 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Sydväst om Branäsberget, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>387836</v>
+        <v>387822</v>
       </c>
       <c r="R55" t="n">
-        <v>6723530</v>
+        <v>6723555</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6310,12 +5889,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Garnlav med apothecier</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6324,71 +5908,67 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Christina Svensson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Christina Svensson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120970925</v>
+        <v>94037181</v>
       </c>
       <c r="B56" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Sydväst om Branäsberget, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>387824</v>
+        <v>388036</v>
       </c>
       <c r="R56" t="n">
-        <v>6723508</v>
+        <v>6723691</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6412,12 +5992,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6432,62 +6012,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Christina Svensson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Christina Svensson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120976728</v>
+        <v>96860863</v>
       </c>
       <c r="B57" t="n">
-        <v>88031</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>386791</v>
+        <v>387695</v>
       </c>
       <c r="R57" t="n">
-        <v>6723204</v>
+        <v>6723577</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6514,12 +6089,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6534,62 +6109,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120976749</v>
+        <v>120970920</v>
       </c>
       <c r="B58" t="n">
-        <v>82388</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>387877</v>
+        <v>388053</v>
       </c>
       <c r="R58" t="n">
-        <v>6723565</v>
+        <v>6723664</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6636,49 +6206,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120970946</v>
+        <v>120970924</v>
       </c>
       <c r="B59" t="n">
-        <v>88031</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6688,10 +6253,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>387338</v>
+        <v>387816</v>
       </c>
       <c r="R59" t="n">
-        <v>6723431</v>
+        <v>6723527</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6750,50 +6315,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120976758</v>
+        <v>120970936</v>
       </c>
       <c r="B60" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>388026</v>
+        <v>386940</v>
       </c>
       <c r="R60" t="n">
-        <v>6723646</v>
+        <v>6723292</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6840,62 +6400,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120976755</v>
+        <v>120970937</v>
       </c>
       <c r="B61" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>387971</v>
+        <v>386898</v>
       </c>
       <c r="R61" t="n">
-        <v>6723631</v>
+        <v>6723285</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6942,62 +6497,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120976735</v>
+        <v>120970939</v>
       </c>
       <c r="B62" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Andersberget, Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>387303</v>
+        <v>386858</v>
       </c>
       <c r="R62" t="n">
-        <v>6723425</v>
+        <v>6723265</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7044,62 +6594,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120970926</v>
+        <v>120976727</v>
       </c>
       <c r="B63" t="n">
-        <v>78638</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>387809</v>
+        <v>386876</v>
       </c>
       <c r="R63" t="n">
-        <v>6723508</v>
+        <v>6723260</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7146,62 +6691,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120970940</v>
+        <v>120976744</v>
       </c>
       <c r="B64" t="n">
-        <v>79714</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>387010</v>
+        <v>387795</v>
       </c>
       <c r="R64" t="n">
-        <v>6723330</v>
+        <v>6723523</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7248,62 +6788,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120970945</v>
+        <v>120976748</v>
       </c>
       <c r="B65" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Andersbergsmyren, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>387254</v>
+        <v>387836</v>
       </c>
       <c r="R65" t="n">
-        <v>6723421</v>
+        <v>6723530</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7350,62 +6885,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121672251</v>
+        <v>120976757</v>
       </c>
       <c r="B66" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>387205</v>
+        <v>388006</v>
       </c>
       <c r="R66" t="n">
-        <v>6723389</v>
+        <v>6723626</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7452,62 +6982,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121672254</v>
+        <v>120976759</v>
       </c>
       <c r="B67" t="n">
-        <v>90745</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>387774</v>
+        <v>388030</v>
       </c>
       <c r="R67" t="n">
-        <v>6723594</v>
+        <v>6723650</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7554,62 +7079,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121672240</v>
+        <v>120976742</v>
       </c>
       <c r="B68" t="n">
-        <v>90763</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>387775</v>
+        <v>387783</v>
       </c>
       <c r="R68" t="n">
-        <v>6723585</v>
+        <v>6723518</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7656,27 +7176,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121672243</v>
+        <v>96860858</v>
       </c>
       <c r="B69" t="n">
-        <v>90763</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7684,34 +7199,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>6450</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>388056</v>
+        <v>387714</v>
       </c>
       <c r="R69" t="n">
-        <v>6723670</v>
+        <v>6723574</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7738,12 +7253,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7758,27 +7273,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121672250</v>
+        <v>96860876</v>
       </c>
       <c r="B70" t="n">
-        <v>78666</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7786,34 +7296,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6450</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>386886</v>
+        <v>387712</v>
       </c>
       <c r="R70" t="n">
-        <v>6723261</v>
+        <v>6723568</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7840,17 +7350,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På björk.</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7865,27 +7370,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121672249</v>
+        <v>96860881</v>
       </c>
       <c r="B71" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7893,34 +7393,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>386886</v>
+        <v>387188</v>
       </c>
       <c r="R71" t="n">
-        <v>6723261</v>
+        <v>6723496</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7947,17 +7447,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På björk.</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7972,27 +7467,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121672239</v>
+        <v>94037173</v>
       </c>
       <c r="B72" t="n">
-        <v>90745</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8000,37 +7490,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Sydväst om Branäsberget, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>387391</v>
+        <v>387964</v>
       </c>
       <c r="R72" t="n">
-        <v>6723451</v>
+        <v>6723679</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8054,12 +7544,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8074,27 +7564,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Christina Svensson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Christina Svensson, Andreas Larsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121672246</v>
+        <v>120976751</v>
       </c>
       <c r="B73" t="n">
-        <v>79714</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8102,34 +7587,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Andersberget, Branäs, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>387932</v>
+        <v>387955</v>
       </c>
       <c r="R73" t="n">
-        <v>6723626</v>
+        <v>6723604</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8176,27 +7661,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121672242</v>
+        <v>121672248</v>
       </c>
       <c r="B74" t="n">
-        <v>74729</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8204,21 +7684,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>308</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8228,10 +7708,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>387833</v>
+        <v>387664</v>
       </c>
       <c r="R74" t="n">
-        <v>6723529</v>
+        <v>6723537</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8290,50 +7770,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121672245</v>
+        <v>85440039</v>
       </c>
       <c r="B75" t="n">
-        <v>79673</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>SO om Villmyren, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>387056</v>
+        <v>387211</v>
       </c>
       <c r="R75" t="n">
-        <v>6723350</v>
+        <v>6723382</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8360,12 +7835,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8380,62 +7855,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm, Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121672247</v>
+        <v>96860867</v>
       </c>
       <c r="B76" t="n">
-        <v>90710</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Ö om Andersberget, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>387273</v>
+        <v>387709</v>
       </c>
       <c r="R76" t="n">
-        <v>6723412</v>
+        <v>6723568</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8462,12 +7932,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2021-10-25</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8482,12 +7952,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8497,12 +7967,7 @@
         <v>121672241</v>
       </c>
       <c r="B77" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8601,37 +8066,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121672252</v>
+        <v>121672249</v>
       </c>
       <c r="B78" t="n">
-        <v>90710</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8641,10 +8101,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>386906</v>
+        <v>386886</v>
       </c>
       <c r="R78" t="n">
-        <v>6723248</v>
+        <v>6723261</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8677,6 +8137,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8703,15 +8168,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121672248</v>
+        <v>121672251</v>
       </c>
       <c r="B79" t="n">
-        <v>79250</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8719,21 +8179,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8743,10 +8203,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>387664</v>
+        <v>387205</v>
       </c>
       <c r="R79" t="n">
-        <v>6723537</v>
+        <v>6723389</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8805,50 +8265,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121672244</v>
+        <v>120970940</v>
       </c>
       <c r="B80" t="n">
-        <v>78666</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>387777</v>
+        <v>387010</v>
       </c>
       <c r="R80" t="n">
-        <v>6723536</v>
+        <v>6723330</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8895,27 +8350,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Boström</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121672255</v>
+        <v>120970943</v>
       </c>
       <c r="B81" t="n">
-        <v>79673</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8923,34 +8373,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>S Branäs, Vrm</t>
+          <t>Andersbergsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>387034</v>
+        <v>387078</v>
       </c>
       <c r="R81" t="n">
-        <v>6723332</v>
+        <v>6723335</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8997,15 +8447,704 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>85440029</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SO om Villmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>387797</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6723514</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2019-03-26</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2019-03-26</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>anders tedeholm, Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>85440031</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SO om Villmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>387818</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6723589</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2019-03-26</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2019-03-26</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>anders tedeholm, Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120976734</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Andersberget, Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>387161</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6723401</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120970933</v>
+      </c>
+      <c r="B85" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Andersbergsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>387048</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6723350</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120970942</v>
+      </c>
+      <c r="B86" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Andersbergsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>387010</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6723330</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>121672245</v>
+      </c>
+      <c r="B87" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>387056</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6723350</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
           <t>Anders Boström</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
+      <c r="AX87" t="inlineStr">
         <is>
           <t>Anders Boström</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr"/>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>121672255</v>
+      </c>
+      <c r="B88" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>S Branäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>387034</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6723332</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28033-2024 artfynd.xlsx
+++ b/artfynd/A 28033-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970931</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976760</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860854</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860873</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860880</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970921</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970922</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970923</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970925</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970926</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970927</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976741</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976743</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976745</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976746</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976752</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976755</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976756</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976758</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672244</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672250</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672242</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860852</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860883</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970946</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970948</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3296,6 +3431,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976728</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976731</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3490,6 +3635,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976736</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3587,6 +3737,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976754</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3684,6 +3839,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976740</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860887</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3878,6 +4043,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672239</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3975,6 +4145,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672253</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4072,6 +4247,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672254</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4169,6 +4349,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860878</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4266,6 +4451,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85440030</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4363,6 +4553,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970928</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4460,6 +4655,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970930</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4557,6 +4757,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976726</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4654,6 +4859,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976730</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4751,6 +4961,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976737</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4848,6 +5063,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976738</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4945,6 +5165,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976749</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5042,6 +5267,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672246</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5139,6 +5369,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037169</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5236,6 +5471,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970934</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5333,6 +5573,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970945</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5430,6 +5675,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976735</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5527,6 +5777,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976747</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5624,6 +5879,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672247</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5721,6 +5981,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672252</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5818,6 +6083,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85440040</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5924,6 +6194,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037179</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6021,6 +6296,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037181</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6118,6 +6398,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860863</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6215,6 +6500,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970920</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6312,6 +6602,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970924</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6409,6 +6704,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970936</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6506,6 +6806,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970937</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6603,6 +6908,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970939</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6700,6 +7010,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976727</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6797,6 +7112,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976744</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6894,6 +7214,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976748</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6991,6 +7316,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976757</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7088,6 +7418,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976759</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7185,6 +7520,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976742</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7282,6 +7622,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860858</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7379,6 +7724,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860876</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7476,6 +7826,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860881</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7573,6 +7928,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94037173</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7670,6 +8030,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976751</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7767,6 +8132,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672248</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7864,6 +8234,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85440039</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7961,6 +8336,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96860867</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8063,6 +8443,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672241</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8165,6 +8550,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672249</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8262,6 +8652,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672251</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8359,6 +8754,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970940</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8456,6 +8856,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970943</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8558,6 +8963,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85440029</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8660,6 +9070,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85440031</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8757,6 +9172,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120976734</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8854,6 +9274,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970933</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8951,6 +9376,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120970942</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9048,6 +9478,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672245</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9145,8 +9580,102 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121672255</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>